--- a/internal/lib/service/excel/templates/res-summary.xlsx
+++ b/internal/lib/service/excel/templates/res-summary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\go\srmt-prime\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\go\srmt-prime\internal\lib\service\excel\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1649496-954D-4DB8-A288-A35A6D0DCE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A065FCBA-07D4-42FC-831C-F35911AFA5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -191,7 +191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="A18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -215,7 +215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="A22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -239,7 +239,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="F22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -263,7 +263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -1702,7 +1702,7 @@
     <xf numFmtId="166" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2204,6 +2204,34 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="19" fillId="15" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="19" fillId="16" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="15" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="16" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="171" fontId="35" fillId="12" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2278,36 +2306,24 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="35" fillId="12" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="173" fontId="19" fillId="15" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="19" fillId="15" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="19" fillId="16" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="15" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="16" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2370,7 +2386,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAA4wJ+AA8AAAAAAAAAHgOSAF8BAADDJgAAOAAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAA4wJ+AA8AAAAAAAAAHgOSAF8BAADDJgAAOAAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2446,7 +2462,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAWAOGAAUAAAAAAAAAkwOaAHYBAAAADwAAOAAAADMAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAWAOGAAUAAAAAAAAAkwOaAHYBAAAADwAAOAAAADMAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2522,7 +2538,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAA5wKIAAsAAAAAAAAAIgObAHsBAAArHQAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAA5wKIAAsAAAAAAAAAIgObAHsBAAArHQAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2598,7 +2614,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAbgKHAAUAAAAAAAAAqAKaAHkBAAA4DgAANQAAADIAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAbgKHAAUAAAAAAAAAqAKaAHkBAAA4DgAANQAAADIAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2674,7 +2690,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAAUgDdAAYAAAAAAAAAywDwAGgCAACyDwAANQAAADIAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAAUgDdAAYAAAAAAAAAywDwAGgCAACyDwAANQAAADIAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2750,7 +2766,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAA5AKDAAcAAAAAAAAAHgOXAG0BAACMEwAAOAAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAA5AKDAAcAAAAAAAAAHgOXAG0BAACMEwAAOAAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2826,7 +2842,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAAxAOCAAcAAAAAAAAA/wOVAGsBAABBFAAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAAxAOCAAcAAAAAAAAA/wOVAGsBAABBFAAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2902,7 +2918,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAgAAAAAAAAATgG1AAgAAAAAAAAAxQHIAPkBAAD1FAAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAgAAAAAAAAATgG1AAgAAAAAAAAAxQHIAPkBAAD1FAAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2978,7 +2994,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAkAAAAAAAAATQODAAkAAAAAAAAAiQOWAG0BAACvGAAANQAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAkAAAAAAAAATQODAAkAAAAAAAAAiQOWAG0BAACvGAAANQAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3054,7 +3070,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAoAAAAAAAAAfACCAAoAAAAAAAAA+ACVAGsBAABwGQAANQAAADEAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAoAAAAAAAAAfACCAAoAAAAAAAAA+ACVAGsBAABwGQAANQAAADEAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3130,7 +3146,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAAywODAA4AAAAAAAAACACWAG0BAACwIgAANQAAAC4AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAAywODAA4AAAAAAAAACACWAG0BAACwIgAANQAAAC4AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3206,7 +3222,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA4AAAAAAAAAOgG1AA4AAAAAAAAAsAHIAPkBAABXIwAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA4AAAAAAAAAOgG1AA4AAAAAAAAAsAHIAPkBAABXIwAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3282,7 +3298,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAI8MAQAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAAxwOBAA8AAAAAAAAAAASUAGgBAAB7JwAANQAAAC4AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAI8MAQAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAAxwOBAA8AAAAAAAAAAASUAGgBAAB7JwAANQAAAC4AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3358,7 +3374,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAABAAAAAAAAAAXQGxABAAAAAAAAAA1AHFAO4BAAAzKAAANwAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAABAAAAAAAAAAXQGxABAAAAAAAAAA1AHFAO4BAAAzKAAANwAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3434,7 +3450,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAAvgOHAAsAAAAAAAAA+QObAHkBAADYHQAANwAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAAvgOHAAsAAAAAAAAA+QObAHkBAADYHQAANwAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3510,7 +3526,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAwAAAAAAAAAPAG9AAwAAAAAAAAAtQHQAA8CAACKHgAANQAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAwAAAAAAAAAPAG9AAwAAAAAAAAAtQHQAA8CAACKHgAANQAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3586,7 +3602,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAA6gKAAA0AAAAAAAAAJgOUAGUBAAD7IQAAOAAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAA6gKAAA0AAAAAAAAAJgOUAGUBAAD7IQAAOAAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3662,7 +3678,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAADgLfAAYAAAAAAAAAhQLyAG4CAABqEAAANQAAADEAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAADgLfAAYAAAAAAAAAhQLyAG4CAABqEAAANQAAADEAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -4000,23 +4016,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:204" ht="29.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="155" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="148"/>
-      <c r="N1" s="148"/>
-      <c r="O1" s="148"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
+      <c r="J1" s="155"/>
+      <c r="K1" s="155"/>
+      <c r="L1" s="155"/>
+      <c r="M1" s="155"/>
+      <c r="N1" s="155"/>
+      <c r="O1" s="155"/>
       <c r="P1" s="132"/>
       <c r="Q1" s="132"/>
       <c r="R1" s="132"/>
@@ -4132,12 +4148,12 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
-      <c r="L2" s="149">
+      <c r="L2" s="156">
         <v>46007</v>
       </c>
-      <c r="M2" s="149"/>
-      <c r="N2" s="149"/>
-      <c r="O2" s="149"/>
+      <c r="M2" s="156"/>
+      <c r="N2" s="156"/>
+      <c r="O2" s="156"/>
       <c r="P2" s="130"/>
       <c r="Q2" s="129"/>
       <c r="R2" s="129"/>
@@ -4238,35 +4254,35 @@
       <c r="FZ2" s="123"/>
     </row>
     <row r="3" spans="1:204" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="164" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="140" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="150" t="s">
+      <c r="C3" s="157" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="151"/>
-      <c r="E3" s="151"/>
-      <c r="F3" s="150" t="s">
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="157" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="151"/>
-      <c r="H3" s="152"/>
-      <c r="I3" s="150" t="s">
+      <c r="G3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="157" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="151"/>
-      <c r="K3" s="152"/>
-      <c r="L3" s="153" t="s">
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="160" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="154"/>
-      <c r="N3" s="153" t="s">
+      <c r="M3" s="161"/>
+      <c r="N3" s="160" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="154"/>
+      <c r="O3" s="161"/>
       <c r="P3" s="24"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
@@ -4364,39 +4380,39 @@
       <c r="FS3" s="123"/>
     </row>
     <row r="4" spans="1:204" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="158"/>
-      <c r="B4" s="162">
+      <c r="A4" s="165"/>
+      <c r="B4" s="169">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="C4" s="164">
+      <c r="C4" s="151">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="D4" s="159" t="s">
+      <c r="D4" s="166" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="160"/>
+      <c r="E4" s="167"/>
       <c r="F4" s="139">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="G4" s="159" t="s">
+      <c r="G4" s="166" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="160"/>
-      <c r="I4" s="164">
+      <c r="H4" s="167"/>
+      <c r="I4" s="151">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="J4" s="159" t="s">
+      <c r="J4" s="166" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="161"/>
-      <c r="L4" s="155"/>
-      <c r="M4" s="156"/>
-      <c r="N4" s="155"/>
-      <c r="O4" s="156"/>
+      <c r="K4" s="168"/>
+      <c r="L4" s="162"/>
+      <c r="M4" s="163"/>
+      <c r="N4" s="162"/>
+      <c r="O4" s="163"/>
       <c r="P4" s="121"/>
       <c r="Q4" s="121"/>
       <c r="R4" s="121"/>
@@ -4493,9 +4509,9 @@
       <c r="DE4" s="4"/>
     </row>
     <row r="5" spans="1:204" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="158"/>
-      <c r="B5" s="163"/>
-      <c r="C5" s="164"/>
+      <c r="A5" s="165"/>
+      <c r="B5" s="170"/>
+      <c r="C5" s="151"/>
       <c r="D5" s="136">
         <f>YEAR($L$2)-1</f>
         <v>2024</v>
@@ -4515,7 +4531,7 @@
         <f>YEAR($L$2)-2</f>
         <v>2023</v>
       </c>
-      <c r="I5" s="164"/>
+      <c r="I5" s="151"/>
       <c r="J5" s="136">
         <f>YEAR($L$2)-1</f>
         <v>2024</v>
@@ -4731,7 +4747,7 @@
       <c r="GV5" s="117"/>
     </row>
     <row r="6" spans="1:204" s="93" customFormat="1" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="165" t="s">
+      <c r="A6" s="148" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="99">
@@ -4967,7 +4983,7 @@
       <c r="GV6" s="106"/>
     </row>
     <row r="7" spans="1:204" ht="21.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="165"/>
+      <c r="A7" s="148"/>
       <c r="B7" s="143" t="s">
         <v>12</v>
       </c>
@@ -5012,11 +5028,11 @@
         <f>IFERROR(L6/M6, 0)</f>
         <v>1</v>
       </c>
-      <c r="N7" s="166">
+      <c r="N7" s="146">
         <f>N6-O6</f>
         <v>0</v>
       </c>
-      <c r="O7" s="167" t="str">
+      <c r="O7" s="147" t="str">
         <f>IF(TEXT(N6-O6,"+0,0; -0,0")="+0,0","0,0",TEXT(N6-O6,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -5211,7 +5227,7 @@
       <c r="GV7" s="113"/>
     </row>
     <row r="8" spans="1:204" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="165" t="s">
+      <c r="A8" s="148" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="99">
@@ -5447,7 +5463,7 @@
       <c r="GV8" s="106"/>
     </row>
     <row r="9" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="165"/>
+      <c r="A9" s="148"/>
       <c r="B9" s="143" t="s">
         <v>16</v>
       </c>
@@ -5492,11 +5508,11 @@
         <f>IFERROR(L8/M8, 0)</f>
         <v>1</v>
       </c>
-      <c r="N9" s="166">
+      <c r="N9" s="146">
         <f>N8-O8</f>
         <v>0</v>
       </c>
-      <c r="O9" s="167" t="str">
+      <c r="O9" s="147" t="str">
         <f>IF(TEXT(N8-O8,"+0,0; -0,0")="+0,0","0,0",TEXT(N8-O8,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -5691,7 +5707,7 @@
       <c r="GV9" s="102"/>
     </row>
     <row r="10" spans="1:204" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="165" t="s">
+      <c r="A10" s="148" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="99">
@@ -5923,7 +5939,7 @@
       <c r="GV10" s="106"/>
     </row>
     <row r="11" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="165"/>
+      <c r="A11" s="148"/>
       <c r="B11" s="143" t="s">
         <v>20</v>
       </c>
@@ -5968,8 +5984,8 @@
         <f>IFERROR(L10/M10, 0)</f>
         <v>1</v>
       </c>
-      <c r="N11" s="168"/>
-      <c r="O11" s="169"/>
+      <c r="N11" s="149"/>
+      <c r="O11" s="150"/>
       <c r="P11" s="89"/>
       <c r="Q11" s="89"/>
       <c r="R11" s="109"/>
@@ -6161,7 +6177,7 @@
       <c r="GV11" s="102"/>
     </row>
     <row r="12" spans="1:204" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="165" t="s">
+      <c r="A12" s="148" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="99">
@@ -6397,7 +6413,7 @@
       <c r="GV12" s="106"/>
     </row>
     <row r="13" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="165"/>
+      <c r="A13" s="148"/>
       <c r="B13" s="143" t="s">
         <v>23</v>
       </c>
@@ -6442,11 +6458,11 @@
         <f>IFERROR(L12/M12, 0)</f>
         <v>1</v>
       </c>
-      <c r="N13" s="166">
+      <c r="N13" s="146">
         <f>N12-O12</f>
         <v>0</v>
       </c>
-      <c r="O13" s="167" t="str">
+      <c r="O13" s="147" t="str">
         <f>IF(TEXT(N12-O12,"+0,0; -0,0")="+0,0","0,0",TEXT(N12-O12,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -6641,7 +6657,7 @@
       <c r="GV13" s="102"/>
     </row>
     <row r="14" spans="1:204" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="165" t="s">
+      <c r="A14" s="148" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="99">
@@ -6877,7 +6893,7 @@
       <c r="GV14" s="106"/>
     </row>
     <row r="15" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="165"/>
+      <c r="A15" s="148"/>
       <c r="B15" s="143" t="s">
         <v>25</v>
       </c>
@@ -6922,11 +6938,11 @@
         <f>IFERROR(L14/M14, 0)</f>
         <v>1</v>
       </c>
-      <c r="N15" s="166">
+      <c r="N15" s="146">
         <f>N14-O14</f>
         <v>0</v>
       </c>
-      <c r="O15" s="167" t="str">
+      <c r="O15" s="147" t="str">
         <f>IF(TEXT(N14-O14,"+0,0; -0,0")="+0,0","0,0",TEXT(N14-O14,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -7121,7 +7137,7 @@
       <c r="GV15" s="102"/>
     </row>
     <row r="16" spans="1:204" s="105" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="165" t="s">
+      <c r="A16" s="172" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="99">
@@ -7357,7 +7373,7 @@
       <c r="GV16" s="106"/>
     </row>
     <row r="17" spans="1:211" s="85" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="165"/>
+      <c r="A17" s="173"/>
       <c r="B17" s="143" t="s">
         <v>29</v>
       </c>
@@ -7402,11 +7418,11 @@
         <f>IFERROR(L16/M16, 0)</f>
         <v>1</v>
       </c>
-      <c r="N17" s="166">
+      <c r="N17" s="146">
         <f>N16-O16</f>
         <v>0</v>
       </c>
-      <c r="O17" s="167" t="str">
+      <c r="O17" s="171" t="str">
         <f>IF(TEXT(N16-O16,"+0,0; -0,0")="+0,0","0,0",TEXT(N16-O16,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -7600,253 +7616,170 @@
       <c r="GU17" s="102"/>
       <c r="GV17" s="102"/>
     </row>
-    <row r="18" spans="1:211" s="93" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="170" t="s">
-        <v>33</v>
+    <row r="18" spans="1:211" s="63" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="145" t="s">
+        <v>37</v>
       </c>
-      <c r="B18" s="99"/>
+      <c r="B18" s="99">
+        <v>1</v>
+      </c>
       <c r="C18" s="99">
-        <f t="shared" ref="C18:M18" si="0">C16+C14+C12+C10+C8+C6</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D18" s="141">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E18" s="142">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F18" s="77">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G18" s="101">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H18" s="100">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1</v>
       </c>
-      <c r="I18" s="77">
-        <f t="shared" si="0"/>
-        <v>6</v>
+      <c r="I18" s="111">
+        <v>1</v>
       </c>
       <c r="J18" s="101">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K18" s="100">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L18" s="99">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M18" s="138">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>0</v>
       </c>
-      <c r="N18" s="77"/>
-      <c r="O18" s="77"/>
-      <c r="P18" s="98"/>
-      <c r="Q18" s="98"/>
-      <c r="R18" s="98"/>
-      <c r="S18" s="97"/>
-      <c r="T18" s="96"/>
-      <c r="U18" s="96"/>
-      <c r="V18" s="96"/>
-      <c r="W18" s="96"/>
-      <c r="X18" s="96"/>
-      <c r="Y18" s="96"/>
-      <c r="Z18" s="96"/>
-      <c r="AA18" s="96"/>
-      <c r="AB18" s="95"/>
-      <c r="AC18" s="95"/>
-      <c r="AD18" s="95"/>
-      <c r="AE18" s="95"/>
-      <c r="AF18" s="95"/>
-      <c r="AG18" s="95"/>
-      <c r="AH18" s="95"/>
-      <c r="AI18" s="95"/>
-      <c r="AJ18" s="95"/>
-      <c r="AK18" s="95"/>
-      <c r="AL18" s="95"/>
-      <c r="AM18" s="95"/>
-      <c r="AN18" s="95"/>
-      <c r="AO18" s="95"/>
-      <c r="AP18" s="95"/>
-      <c r="AQ18" s="95"/>
-      <c r="AR18" s="95"/>
-      <c r="AS18" s="95"/>
-      <c r="AT18" s="94"/>
-      <c r="AU18" s="94"/>
-      <c r="AV18" s="94"/>
-      <c r="AW18" s="94"/>
-      <c r="AX18" s="94"/>
-      <c r="AY18" s="94"/>
-      <c r="AZ18" s="94"/>
-      <c r="BA18" s="94"/>
-      <c r="BB18" s="94"/>
-      <c r="BC18" s="94"/>
-      <c r="BD18" s="94"/>
-      <c r="BE18" s="94"/>
-      <c r="BF18" s="95"/>
-      <c r="BG18" s="95"/>
-      <c r="BH18" s="95"/>
-      <c r="BI18" s="95"/>
-      <c r="BJ18" s="95"/>
-      <c r="BK18" s="95"/>
-      <c r="BL18" s="95"/>
-      <c r="BM18" s="95"/>
-      <c r="BN18" s="95"/>
-      <c r="BO18" s="95"/>
-      <c r="BP18" s="95"/>
-      <c r="BQ18" s="95"/>
-      <c r="BR18" s="95"/>
-      <c r="BS18" s="95"/>
-      <c r="BT18" s="95"/>
-      <c r="BU18" s="95"/>
-      <c r="BV18" s="95"/>
-      <c r="BW18" s="95"/>
-      <c r="BX18" s="95"/>
-      <c r="BY18" s="95"/>
-      <c r="BZ18" s="95"/>
-      <c r="CA18" s="95"/>
-      <c r="CB18" s="95"/>
-      <c r="CC18" s="95"/>
-      <c r="CD18" s="95"/>
-      <c r="CE18" s="95"/>
-      <c r="CF18" s="95"/>
-      <c r="CG18" s="95"/>
-      <c r="CH18" s="95"/>
-      <c r="CI18" s="95"/>
-      <c r="CJ18" s="95"/>
-      <c r="CK18" s="95"/>
-      <c r="CL18" s="95"/>
-      <c r="CM18" s="95"/>
-      <c r="CN18" s="95"/>
-      <c r="CO18" s="95"/>
-      <c r="CP18" s="95"/>
-      <c r="CQ18" s="95"/>
-      <c r="CR18" s="95"/>
-      <c r="CS18" s="95"/>
-      <c r="CT18" s="95"/>
-      <c r="CU18" s="95"/>
-      <c r="CV18" s="95"/>
-      <c r="CW18" s="95"/>
-      <c r="CX18" s="95"/>
-      <c r="CY18" s="95"/>
-      <c r="CZ18" s="95"/>
-      <c r="DA18" s="95"/>
-      <c r="DB18" s="95"/>
-      <c r="DC18" s="95"/>
-      <c r="DD18" s="95"/>
-      <c r="DE18" s="95"/>
-      <c r="DF18" s="95"/>
-      <c r="DG18" s="95"/>
-      <c r="DH18" s="95"/>
-      <c r="DI18" s="95"/>
-      <c r="DJ18" s="95"/>
-      <c r="DK18" s="95"/>
-      <c r="DL18" s="95"/>
-      <c r="DM18" s="95"/>
-      <c r="DN18" s="95"/>
-      <c r="DO18" s="95"/>
-      <c r="DP18" s="95"/>
-      <c r="DQ18" s="95"/>
-      <c r="DR18" s="95"/>
-      <c r="DS18" s="95"/>
-      <c r="DT18" s="95"/>
-      <c r="DU18" s="95"/>
-      <c r="DV18" s="95"/>
-      <c r="DW18" s="95"/>
-      <c r="DX18" s="95"/>
-      <c r="DY18" s="95"/>
-      <c r="DZ18" s="95"/>
-      <c r="EA18" s="95"/>
-      <c r="EB18" s="95"/>
-      <c r="EC18" s="95"/>
-      <c r="ED18" s="95"/>
-      <c r="EE18" s="95"/>
-      <c r="EF18" s="95"/>
-      <c r="EG18" s="95"/>
-      <c r="EH18" s="94"/>
-      <c r="EI18" s="94"/>
-      <c r="EJ18" s="94"/>
-      <c r="EK18" s="94"/>
-      <c r="EL18" s="94"/>
-      <c r="EM18" s="94"/>
-      <c r="EN18" s="94"/>
-      <c r="EO18" s="94"/>
-      <c r="EP18" s="94"/>
-      <c r="EQ18" s="94"/>
-      <c r="ER18" s="94"/>
-      <c r="ES18" s="94"/>
-      <c r="ET18" s="94"/>
-      <c r="EU18" s="94"/>
-      <c r="EV18" s="94"/>
-      <c r="EW18" s="94"/>
-      <c r="EX18" s="94"/>
-      <c r="EY18" s="94"/>
-      <c r="EZ18" s="94"/>
-      <c r="FA18" s="94"/>
-      <c r="FB18" s="94"/>
-      <c r="FC18" s="94"/>
-      <c r="FD18" s="94"/>
-      <c r="FE18" s="94"/>
-      <c r="FF18" s="94"/>
-      <c r="FG18" s="94"/>
-      <c r="FH18" s="94"/>
-      <c r="FI18" s="94"/>
-      <c r="FJ18" s="94"/>
-      <c r="FK18" s="94"/>
-      <c r="FL18" s="94"/>
-      <c r="FM18" s="94"/>
-      <c r="FN18" s="94"/>
-      <c r="FO18" s="94"/>
-      <c r="FP18" s="94"/>
-      <c r="FQ18" s="94"/>
-      <c r="FR18" s="94"/>
-      <c r="FS18" s="94"/>
-      <c r="FT18" s="94"/>
-      <c r="FU18" s="94"/>
-      <c r="FV18" s="94"/>
-      <c r="FW18" s="94"/>
-      <c r="FX18" s="94"/>
-      <c r="FY18" s="94"/>
-      <c r="FZ18" s="94"/>
-      <c r="GA18" s="94"/>
-      <c r="GB18" s="94"/>
-      <c r="GC18" s="94"/>
-      <c r="GD18" s="94"/>
-      <c r="GE18" s="94"/>
-      <c r="GF18" s="94"/>
-      <c r="GG18" s="94"/>
-      <c r="GH18" s="94"/>
-      <c r="GI18" s="94"/>
-      <c r="GJ18" s="94"/>
-      <c r="GK18" s="94"/>
-      <c r="GL18" s="94"/>
-      <c r="GM18" s="94"/>
-      <c r="GN18" s="94"/>
-      <c r="GO18" s="94"/>
-      <c r="GP18" s="94"/>
-      <c r="GQ18" s="94"/>
-      <c r="GR18" s="94"/>
-      <c r="GS18" s="94"/>
-      <c r="GT18" s="94"/>
-      <c r="GU18" s="94"/>
-      <c r="GV18" s="94"/>
-    </row>
-    <row r="19" spans="1:211" s="85" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="170"/>
-      <c r="B19" s="143"/>
-      <c r="C19" s="143">
-        <f>C7+C9+C11+C13+C15+C17</f>
-        <v>1.870000000000001</v>
+      <c r="N18" s="77">
+        <v>1</v>
+      </c>
+      <c r="O18" s="76">
+        <v>1</v>
+      </c>
+      <c r="P18" s="75"/>
+      <c r="Q18" s="74"/>
+      <c r="R18" s="74"/>
+      <c r="S18" s="65"/>
+      <c r="T18" s="65"/>
+      <c r="U18" s="65"/>
+      <c r="V18" s="65"/>
+      <c r="W18" s="65"/>
+      <c r="X18" s="65"/>
+      <c r="Y18" s="65"/>
+      <c r="Z18" s="65"/>
+      <c r="AA18" s="65"/>
+      <c r="AB18" s="65"/>
+      <c r="AC18" s="65"/>
+      <c r="AD18" s="65"/>
+      <c r="AE18" s="65"/>
+      <c r="AF18" s="65"/>
+      <c r="AG18" s="65"/>
+      <c r="AH18" s="65"/>
+      <c r="AI18" s="65"/>
+      <c r="AJ18" s="65"/>
+      <c r="AK18" s="65"/>
+      <c r="AL18" s="65"/>
+      <c r="AM18" s="65"/>
+      <c r="AN18" s="65"/>
+      <c r="AO18" s="65"/>
+      <c r="AP18" s="65"/>
+      <c r="AQ18" s="65"/>
+      <c r="AR18" s="65"/>
+      <c r="AS18" s="65"/>
+      <c r="AT18" s="65"/>
+      <c r="AU18" s="65"/>
+      <c r="AV18" s="65"/>
+      <c r="AW18" s="65"/>
+      <c r="AX18" s="65"/>
+      <c r="AY18" s="65"/>
+      <c r="AZ18" s="65"/>
+      <c r="BA18" s="65"/>
+      <c r="BB18" s="65"/>
+      <c r="BC18" s="65"/>
+      <c r="BD18" s="65"/>
+      <c r="BE18" s="65"/>
+      <c r="BF18" s="66"/>
+      <c r="BG18" s="66"/>
+      <c r="BH18" s="66"/>
+      <c r="BI18" s="66"/>
+      <c r="BJ18" s="66"/>
+      <c r="BK18" s="66"/>
+      <c r="BL18" s="66"/>
+      <c r="BM18" s="66"/>
+      <c r="BN18" s="66"/>
+      <c r="BO18" s="66"/>
+      <c r="BP18" s="66"/>
+      <c r="BQ18" s="66"/>
+      <c r="BR18" s="66"/>
+      <c r="BS18" s="66"/>
+      <c r="BT18" s="66"/>
+      <c r="BU18" s="66"/>
+      <c r="BV18" s="66"/>
+      <c r="BW18" s="66"/>
+      <c r="BX18" s="66"/>
+      <c r="BY18" s="66"/>
+      <c r="BZ18" s="66"/>
+      <c r="CA18" s="66"/>
+      <c r="CB18" s="66"/>
+      <c r="CC18" s="66"/>
+      <c r="CD18" s="66"/>
+      <c r="CE18" s="65"/>
+      <c r="CF18" s="65"/>
+      <c r="CG18" s="65"/>
+      <c r="CH18" s="65"/>
+      <c r="CI18" s="65"/>
+      <c r="CJ18" s="65"/>
+      <c r="CK18" s="65"/>
+      <c r="CL18" s="65"/>
+      <c r="CM18" s="65"/>
+      <c r="CN18" s="65"/>
+      <c r="CO18" s="65"/>
+      <c r="CP18" s="65"/>
+      <c r="CQ18" s="65"/>
+      <c r="CR18" s="65"/>
+      <c r="CS18" s="65"/>
+      <c r="CT18" s="65"/>
+      <c r="CU18" s="65"/>
+      <c r="CV18" s="65"/>
+      <c r="CW18" s="65"/>
+      <c r="CX18" s="65"/>
+      <c r="CY18" s="65"/>
+      <c r="CZ18" s="65"/>
+      <c r="DA18" s="65"/>
+      <c r="DB18" s="65"/>
+      <c r="DC18" s="65"/>
+      <c r="DD18" s="65"/>
+      <c r="DE18" s="65"/>
+      <c r="DF18" s="64"/>
+      <c r="DI18" s="55"/>
+      <c r="DJ18" s="55"/>
+      <c r="DK18" s="55"/>
+      <c r="DL18" s="55"/>
+      <c r="DM18" s="55"/>
+      <c r="DN18" s="55"/>
+      <c r="DO18" s="55"/>
+      <c r="DP18" s="55"/>
+      <c r="DQ18" s="55"/>
+      <c r="DR18" s="55"/>
+      <c r="DS18" s="55"/>
+      <c r="DT18" s="55"/>
+      <c r="DU18" s="55"/>
+      <c r="DV18" s="55"/>
+      <c r="DW18" s="55"/>
+    </row>
+    <row r="19" spans="1:211" s="55" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="145"/>
+      <c r="B19" s="143" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="143" t="s">
+        <v>30</v>
       </c>
       <c r="D19" s="143">
         <f>C18-D18</f>
@@ -7856,9 +7789,8 @@
         <f>C18-E18</f>
         <v>0</v>
       </c>
-      <c r="F19" s="144">
-        <f>F7+F9+F11+F13+F15+F17</f>
-        <v>-13.14</v>
+      <c r="F19" s="144" t="s">
+        <v>31</v>
       </c>
       <c r="G19" s="144">
         <f>F18-G18</f>
@@ -7868,9 +7800,8 @@
         <f>F18-H18</f>
         <v>0</v>
       </c>
-      <c r="I19" s="144">
-        <f>I7+I9+I11+I13+I15+I17</f>
-        <v>83</v>
+      <c r="I19" s="144" t="s">
+        <v>32</v>
       </c>
       <c r="J19" s="144">
         <f>I18-J18</f>
@@ -7878,7 +7809,7 @@
       </c>
       <c r="K19" s="144">
         <f>I18-K18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="143">
         <f>L18-M18</f>
@@ -7886,400 +7817,500 @@
       </c>
       <c r="M19" s="92">
         <f>IFERROR(L18/M18, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="N19" s="91"/>
-      <c r="O19" s="90"/>
-      <c r="P19" s="89"/>
-      <c r="Q19" s="89"/>
-      <c r="R19" s="89"/>
-      <c r="S19" s="89"/>
-      <c r="T19" s="88"/>
-      <c r="U19" s="88"/>
-      <c r="V19" s="88"/>
-      <c r="W19" s="88"/>
-      <c r="X19" s="88"/>
-      <c r="Y19" s="88"/>
-      <c r="Z19" s="86"/>
-      <c r="AA19" s="86"/>
-      <c r="AB19" s="86"/>
-      <c r="AC19" s="86"/>
-      <c r="AD19" s="86"/>
-      <c r="AE19" s="86"/>
-      <c r="AF19" s="86"/>
-      <c r="AG19" s="86"/>
-      <c r="AH19" s="86"/>
-      <c r="AI19" s="86"/>
-      <c r="AJ19" s="86"/>
-      <c r="AK19" s="86"/>
-      <c r="AL19" s="86"/>
-      <c r="AM19" s="86"/>
-      <c r="AN19" s="86"/>
-      <c r="AO19" s="86"/>
-      <c r="AP19" s="86"/>
-      <c r="AQ19" s="86"/>
-      <c r="AR19" s="86"/>
-      <c r="AS19" s="86"/>
-      <c r="AT19" s="86"/>
-      <c r="AU19" s="86"/>
-      <c r="AV19" s="86"/>
-      <c r="AW19" s="86"/>
-      <c r="AX19" s="86"/>
-      <c r="AY19" s="86"/>
-      <c r="AZ19" s="86"/>
-      <c r="BA19" s="86"/>
-      <c r="BB19" s="86"/>
-      <c r="BC19" s="86"/>
-      <c r="BD19" s="86"/>
-      <c r="BE19" s="86"/>
-      <c r="BF19" s="87"/>
-      <c r="BG19" s="87"/>
-      <c r="BH19" s="87"/>
-      <c r="BI19" s="87"/>
-      <c r="BJ19" s="87"/>
-      <c r="BK19" s="87"/>
-      <c r="BL19" s="87"/>
-      <c r="BM19" s="87"/>
-      <c r="BN19" s="87"/>
-      <c r="BO19" s="87"/>
-      <c r="BP19" s="87"/>
-      <c r="BQ19" s="87"/>
-      <c r="BR19" s="87"/>
-      <c r="BS19" s="87"/>
-      <c r="BT19" s="87"/>
-      <c r="BU19" s="87"/>
-      <c r="BV19" s="87"/>
-      <c r="BW19" s="87"/>
-      <c r="BX19" s="87"/>
-      <c r="BY19" s="87"/>
-      <c r="BZ19" s="87"/>
-      <c r="CA19" s="87"/>
-      <c r="CB19" s="87"/>
-      <c r="CC19" s="87"/>
-      <c r="CD19" s="87"/>
-      <c r="CE19" s="86"/>
-      <c r="CF19" s="86"/>
-      <c r="CG19" s="86"/>
-      <c r="CH19" s="86"/>
-      <c r="CI19" s="86"/>
-      <c r="CJ19" s="86"/>
-      <c r="CK19" s="86"/>
-      <c r="CL19" s="86"/>
-      <c r="CM19" s="86"/>
-      <c r="CN19" s="86"/>
-      <c r="CO19" s="86"/>
-      <c r="CP19" s="86"/>
-      <c r="CQ19" s="86"/>
-      <c r="CR19" s="86"/>
-      <c r="CS19" s="86"/>
-      <c r="CT19" s="86"/>
-      <c r="CU19" s="86"/>
-      <c r="CV19" s="86"/>
-      <c r="CW19" s="86"/>
-      <c r="CX19" s="86"/>
-      <c r="CY19" s="86"/>
-      <c r="CZ19" s="86"/>
-      <c r="DA19" s="86"/>
-      <c r="DB19" s="86"/>
-      <c r="DC19" s="86"/>
-      <c r="DD19" s="86"/>
-      <c r="DE19" s="86"/>
-    </row>
-    <row r="20" spans="1:211" s="80" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="171" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="99">
-        <v>1</v>
-      </c>
-      <c r="C20" s="99">
-        <v>1</v>
-      </c>
-      <c r="D20" s="141">
-        <v>1</v>
-      </c>
-      <c r="E20" s="142">
-        <v>1</v>
-      </c>
-      <c r="F20" s="77">
-        <v>1</v>
-      </c>
-      <c r="G20" s="101">
-        <v>1</v>
-      </c>
-      <c r="H20" s="100">
-        <v>1</v>
-      </c>
-      <c r="I20" s="77">
-        <v>1</v>
-      </c>
-      <c r="J20" s="101">
-        <v>1</v>
-      </c>
-      <c r="K20" s="100">
         <v>0</v>
       </c>
-      <c r="L20" s="99">
+      <c r="N19" s="146">
+        <f>N18-O18</f>
         <v>0</v>
       </c>
-      <c r="M20" s="138">
-        <v>0</v>
+      <c r="O19" s="147" t="str">
+        <f>IF(TEXT(N18-O18,"+0,0; -0,0")="+0,0","0,0",TEXT(N18-O18,"+0,0; -0,0"))</f>
+        <v>0,0</v>
       </c>
-      <c r="N20" s="77">
-        <v>1</v>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="56"/>
+      <c r="R19" s="56"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+      <c r="AA19" s="57"/>
+      <c r="AB19" s="57"/>
+      <c r="AC19" s="57"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
+      <c r="AH19" s="57"/>
+      <c r="AI19" s="57"/>
+      <c r="AJ19" s="57"/>
+      <c r="AK19" s="57"/>
+      <c r="AL19" s="57"/>
+      <c r="AM19" s="57"/>
+      <c r="AN19" s="57"/>
+      <c r="AO19" s="57"/>
+      <c r="AP19" s="57"/>
+      <c r="AQ19" s="57"/>
+      <c r="AR19" s="57"/>
+      <c r="AS19" s="57"/>
+      <c r="AT19" s="57"/>
+      <c r="AU19" s="57"/>
+      <c r="AV19" s="57"/>
+      <c r="AW19" s="57"/>
+      <c r="AX19" s="57"/>
+      <c r="AY19" s="57"/>
+      <c r="AZ19" s="57"/>
+      <c r="BA19" s="57"/>
+      <c r="BB19" s="57"/>
+      <c r="BC19" s="57"/>
+      <c r="BD19" s="57"/>
+      <c r="BE19" s="57"/>
+      <c r="BF19" s="6"/>
+      <c r="BG19" s="6"/>
+      <c r="BH19" s="6"/>
+      <c r="BI19" s="6"/>
+      <c r="BJ19" s="6"/>
+      <c r="BK19" s="6"/>
+      <c r="BL19" s="6"/>
+      <c r="BM19" s="6"/>
+      <c r="BN19" s="6"/>
+      <c r="BO19" s="6"/>
+      <c r="BP19" s="6"/>
+      <c r="BQ19" s="6"/>
+      <c r="BR19" s="6"/>
+      <c r="BS19" s="6"/>
+      <c r="BT19" s="6"/>
+      <c r="BU19" s="6"/>
+      <c r="BV19" s="6"/>
+      <c r="BW19" s="6"/>
+      <c r="BX19" s="6"/>
+      <c r="BY19" s="6"/>
+      <c r="BZ19" s="6"/>
+      <c r="CA19" s="6"/>
+      <c r="CB19" s="6"/>
+      <c r="CC19" s="6"/>
+      <c r="CD19" s="6"/>
+      <c r="CE19" s="57"/>
+      <c r="CF19" s="57"/>
+      <c r="CG19" s="57"/>
+      <c r="CH19" s="57"/>
+      <c r="CI19" s="57"/>
+      <c r="CJ19" s="57"/>
+      <c r="CK19" s="57"/>
+      <c r="CL19" s="57"/>
+      <c r="CM19" s="57"/>
+      <c r="CN19" s="57"/>
+      <c r="CO19" s="57"/>
+      <c r="CP19" s="57"/>
+      <c r="CQ19" s="57"/>
+      <c r="CR19" s="57"/>
+      <c r="CS19" s="57"/>
+      <c r="CT19" s="57"/>
+      <c r="CU19" s="57"/>
+      <c r="CV19" s="57"/>
+      <c r="CW19" s="57"/>
+      <c r="CX19" s="57"/>
+      <c r="CY19" s="57"/>
+      <c r="CZ19" s="57"/>
+      <c r="DA19" s="57"/>
+      <c r="DB19" s="57"/>
+      <c r="DC19" s="57"/>
+      <c r="DD19" s="57"/>
+      <c r="DE19" s="57"/>
+      <c r="DF19" s="56"/>
+    </row>
+    <row r="20" spans="1:211" s="93" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="174" t="s">
+        <v>33</v>
       </c>
-      <c r="O20" s="76">
-        <v>1</v>
+      <c r="B20" s="99"/>
+      <c r="C20" s="99">
+        <f>C16+C14+C12+C10+C8+C6+C18</f>
+        <v>7</v>
       </c>
-      <c r="P20" s="84"/>
-      <c r="Q20" s="84"/>
-      <c r="R20" s="84"/>
-      <c r="S20" s="84"/>
-      <c r="T20" s="82"/>
-      <c r="U20" s="82"/>
-      <c r="V20" s="82"/>
-      <c r="W20" s="82"/>
-      <c r="X20" s="82"/>
-      <c r="Y20" s="82"/>
-      <c r="Z20" s="82"/>
-      <c r="AA20" s="82"/>
-      <c r="AB20" s="82"/>
-      <c r="AC20" s="82"/>
-      <c r="AD20" s="82"/>
-      <c r="AE20" s="82"/>
-      <c r="AF20" s="82"/>
-      <c r="AG20" s="82"/>
-      <c r="AH20" s="82"/>
-      <c r="AI20" s="82"/>
-      <c r="AJ20" s="82"/>
-      <c r="AK20" s="82"/>
-      <c r="AL20" s="82"/>
-      <c r="AM20" s="82"/>
-      <c r="AN20" s="82"/>
-      <c r="AO20" s="82"/>
-      <c r="AP20" s="82"/>
-      <c r="AQ20" s="82"/>
-      <c r="AR20" s="82"/>
-      <c r="AS20" s="82"/>
-      <c r="AT20" s="82"/>
-      <c r="AU20" s="82"/>
-      <c r="AV20" s="82"/>
-      <c r="AW20" s="82"/>
-      <c r="AX20" s="82"/>
-      <c r="AY20" s="82"/>
-      <c r="AZ20" s="82"/>
-      <c r="BA20" s="82"/>
-      <c r="BB20" s="82"/>
-      <c r="BC20" s="82"/>
-      <c r="BD20" s="82"/>
-      <c r="BE20" s="82"/>
-      <c r="BF20" s="83"/>
-      <c r="BG20" s="83"/>
-      <c r="BH20" s="83"/>
-      <c r="BI20" s="83"/>
-      <c r="BJ20" s="83"/>
-      <c r="BK20" s="83"/>
-      <c r="BL20" s="83"/>
-      <c r="BM20" s="83"/>
-      <c r="BN20" s="83"/>
-      <c r="BO20" s="83"/>
-      <c r="BP20" s="83"/>
-      <c r="BQ20" s="83"/>
-      <c r="BR20" s="83"/>
-      <c r="BS20" s="83"/>
-      <c r="BT20" s="83"/>
-      <c r="BU20" s="83"/>
-      <c r="BV20" s="83"/>
-      <c r="BW20" s="83"/>
-      <c r="BX20" s="83"/>
-      <c r="BY20" s="83"/>
-      <c r="BZ20" s="83"/>
-      <c r="CA20" s="83"/>
-      <c r="CB20" s="83"/>
-      <c r="CC20" s="83"/>
-      <c r="CD20" s="83"/>
-      <c r="CE20" s="82"/>
-      <c r="CF20" s="82"/>
-      <c r="CG20" s="82"/>
-      <c r="CH20" s="82"/>
-      <c r="CI20" s="82"/>
-      <c r="CJ20" s="82"/>
-      <c r="CK20" s="82"/>
-      <c r="CL20" s="82"/>
-      <c r="CM20" s="82"/>
-      <c r="CN20" s="82"/>
-      <c r="CO20" s="82"/>
-      <c r="CP20" s="82"/>
-      <c r="CQ20" s="82"/>
-      <c r="CR20" s="82"/>
-      <c r="CS20" s="82"/>
-      <c r="CT20" s="82"/>
-      <c r="CU20" s="82"/>
-      <c r="CV20" s="82"/>
-      <c r="CW20" s="82"/>
-      <c r="CX20" s="82"/>
-      <c r="CY20" s="82"/>
-      <c r="CZ20" s="82"/>
-      <c r="DA20" s="82"/>
-      <c r="DB20" s="82"/>
-      <c r="DC20" s="82"/>
-      <c r="DD20" s="82"/>
-      <c r="DE20" s="82"/>
-      <c r="FQ20" s="81"/>
-    </row>
-    <row r="21" spans="1:211" s="55" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="171"/>
-      <c r="B21" s="143" t="s">
-        <v>35</v>
+      <c r="D20" s="99">
+        <f t="shared" ref="D20:M20" si="0">D16+D14+D12+D10+D8+D6+D18</f>
+        <v>7</v>
       </c>
-      <c r="C21" s="143" t="s">
-        <v>39</v>
+      <c r="E20" s="99">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="F20" s="99">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G20" s="99">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="H20" s="99">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="I20" s="99">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="J20" s="99">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="K20" s="99">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="L20" s="99">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="M20" s="99">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="N20" s="77"/>
+      <c r="O20" s="77"/>
+      <c r="P20" s="98"/>
+      <c r="Q20" s="98"/>
+      <c r="R20" s="98"/>
+      <c r="S20" s="97"/>
+      <c r="T20" s="96"/>
+      <c r="U20" s="96"/>
+      <c r="V20" s="96"/>
+      <c r="W20" s="96"/>
+      <c r="X20" s="96"/>
+      <c r="Y20" s="96"/>
+      <c r="Z20" s="96"/>
+      <c r="AA20" s="96"/>
+      <c r="AB20" s="95"/>
+      <c r="AC20" s="95"/>
+      <c r="AD20" s="95"/>
+      <c r="AE20" s="95"/>
+      <c r="AF20" s="95"/>
+      <c r="AG20" s="95"/>
+      <c r="AH20" s="95"/>
+      <c r="AI20" s="95"/>
+      <c r="AJ20" s="95"/>
+      <c r="AK20" s="95"/>
+      <c r="AL20" s="95"/>
+      <c r="AM20" s="95"/>
+      <c r="AN20" s="95"/>
+      <c r="AO20" s="95"/>
+      <c r="AP20" s="95"/>
+      <c r="AQ20" s="95"/>
+      <c r="AR20" s="95"/>
+      <c r="AS20" s="95"/>
+      <c r="AT20" s="94"/>
+      <c r="AU20" s="94"/>
+      <c r="AV20" s="94"/>
+      <c r="AW20" s="94"/>
+      <c r="AX20" s="94"/>
+      <c r="AY20" s="94"/>
+      <c r="AZ20" s="94"/>
+      <c r="BA20" s="94"/>
+      <c r="BB20" s="94"/>
+      <c r="BC20" s="94"/>
+      <c r="BD20" s="94"/>
+      <c r="BE20" s="94"/>
+      <c r="BF20" s="95"/>
+      <c r="BG20" s="95"/>
+      <c r="BH20" s="95"/>
+      <c r="BI20" s="95"/>
+      <c r="BJ20" s="95"/>
+      <c r="BK20" s="95"/>
+      <c r="BL20" s="95"/>
+      <c r="BM20" s="95"/>
+      <c r="BN20" s="95"/>
+      <c r="BO20" s="95"/>
+      <c r="BP20" s="95"/>
+      <c r="BQ20" s="95"/>
+      <c r="BR20" s="95"/>
+      <c r="BS20" s="95"/>
+      <c r="BT20" s="95"/>
+      <c r="BU20" s="95"/>
+      <c r="BV20" s="95"/>
+      <c r="BW20" s="95"/>
+      <c r="BX20" s="95"/>
+      <c r="BY20" s="95"/>
+      <c r="BZ20" s="95"/>
+      <c r="CA20" s="95"/>
+      <c r="CB20" s="95"/>
+      <c r="CC20" s="95"/>
+      <c r="CD20" s="95"/>
+      <c r="CE20" s="95"/>
+      <c r="CF20" s="95"/>
+      <c r="CG20" s="95"/>
+      <c r="CH20" s="95"/>
+      <c r="CI20" s="95"/>
+      <c r="CJ20" s="95"/>
+      <c r="CK20" s="95"/>
+      <c r="CL20" s="95"/>
+      <c r="CM20" s="95"/>
+      <c r="CN20" s="95"/>
+      <c r="CO20" s="95"/>
+      <c r="CP20" s="95"/>
+      <c r="CQ20" s="95"/>
+      <c r="CR20" s="95"/>
+      <c r="CS20" s="95"/>
+      <c r="CT20" s="95"/>
+      <c r="CU20" s="95"/>
+      <c r="CV20" s="95"/>
+      <c r="CW20" s="95"/>
+      <c r="CX20" s="95"/>
+      <c r="CY20" s="95"/>
+      <c r="CZ20" s="95"/>
+      <c r="DA20" s="95"/>
+      <c r="DB20" s="95"/>
+      <c r="DC20" s="95"/>
+      <c r="DD20" s="95"/>
+      <c r="DE20" s="95"/>
+      <c r="DF20" s="95"/>
+      <c r="DG20" s="95"/>
+      <c r="DH20" s="95"/>
+      <c r="DI20" s="95"/>
+      <c r="DJ20" s="95"/>
+      <c r="DK20" s="95"/>
+      <c r="DL20" s="95"/>
+      <c r="DM20" s="95"/>
+      <c r="DN20" s="95"/>
+      <c r="DO20" s="95"/>
+      <c r="DP20" s="95"/>
+      <c r="DQ20" s="95"/>
+      <c r="DR20" s="95"/>
+      <c r="DS20" s="95"/>
+      <c r="DT20" s="95"/>
+      <c r="DU20" s="95"/>
+      <c r="DV20" s="95"/>
+      <c r="DW20" s="95"/>
+      <c r="DX20" s="95"/>
+      <c r="DY20" s="95"/>
+      <c r="DZ20" s="95"/>
+      <c r="EA20" s="95"/>
+      <c r="EB20" s="95"/>
+      <c r="EC20" s="95"/>
+      <c r="ED20" s="95"/>
+      <c r="EE20" s="95"/>
+      <c r="EF20" s="95"/>
+      <c r="EG20" s="95"/>
+      <c r="EH20" s="94"/>
+      <c r="EI20" s="94"/>
+      <c r="EJ20" s="94"/>
+      <c r="EK20" s="94"/>
+      <c r="EL20" s="94"/>
+      <c r="EM20" s="94"/>
+      <c r="EN20" s="94"/>
+      <c r="EO20" s="94"/>
+      <c r="EP20" s="94"/>
+      <c r="EQ20" s="94"/>
+      <c r="ER20" s="94"/>
+      <c r="ES20" s="94"/>
+      <c r="ET20" s="94"/>
+      <c r="EU20" s="94"/>
+      <c r="EV20" s="94"/>
+      <c r="EW20" s="94"/>
+      <c r="EX20" s="94"/>
+      <c r="EY20" s="94"/>
+      <c r="EZ20" s="94"/>
+      <c r="FA20" s="94"/>
+      <c r="FB20" s="94"/>
+      <c r="FC20" s="94"/>
+      <c r="FD20" s="94"/>
+      <c r="FE20" s="94"/>
+      <c r="FF20" s="94"/>
+      <c r="FG20" s="94"/>
+      <c r="FH20" s="94"/>
+      <c r="FI20" s="94"/>
+      <c r="FJ20" s="94"/>
+      <c r="FK20" s="94"/>
+      <c r="FL20" s="94"/>
+      <c r="FM20" s="94"/>
+      <c r="FN20" s="94"/>
+      <c r="FO20" s="94"/>
+      <c r="FP20" s="94"/>
+      <c r="FQ20" s="94"/>
+      <c r="FR20" s="94"/>
+      <c r="FS20" s="94"/>
+      <c r="FT20" s="94"/>
+      <c r="FU20" s="94"/>
+      <c r="FV20" s="94"/>
+      <c r="FW20" s="94"/>
+      <c r="FX20" s="94"/>
+      <c r="FY20" s="94"/>
+      <c r="FZ20" s="94"/>
+      <c r="GA20" s="94"/>
+      <c r="GB20" s="94"/>
+      <c r="GC20" s="94"/>
+      <c r="GD20" s="94"/>
+      <c r="GE20" s="94"/>
+      <c r="GF20" s="94"/>
+      <c r="GG20" s="94"/>
+      <c r="GH20" s="94"/>
+      <c r="GI20" s="94"/>
+      <c r="GJ20" s="94"/>
+      <c r="GK20" s="94"/>
+      <c r="GL20" s="94"/>
+      <c r="GM20" s="94"/>
+      <c r="GN20" s="94"/>
+      <c r="GO20" s="94"/>
+      <c r="GP20" s="94"/>
+      <c r="GQ20" s="94"/>
+      <c r="GR20" s="94"/>
+      <c r="GS20" s="94"/>
+      <c r="GT20" s="94"/>
+      <c r="GU20" s="94"/>
+      <c r="GV20" s="94"/>
+    </row>
+    <row r="21" spans="1:211" s="85" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="175"/>
+      <c r="B21" s="143"/>
+      <c r="C21" s="143">
+        <f>C7+C9+C11+C13+C15+C17+C19</f>
+        <v>-6.5299999999999994</v>
       </c>
       <c r="D21" s="143">
-        <f>C20-D20</f>
+        <f t="shared" ref="D21:M21" si="1">D7+D9+D11+D13+D15+D17+D19</f>
         <v>0</v>
       </c>
       <c r="E21" s="143">
-        <f>C20-E20</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F21" s="144" t="s">
-        <v>36</v>
+      <c r="F21" s="143">
+        <f t="shared" si="1"/>
+        <v>-27.14</v>
       </c>
-      <c r="G21" s="144">
-        <f>F20-G20</f>
+      <c r="G21" s="143">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H21" s="144">
-        <f>F20-H20</f>
+      <c r="H21" s="143">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I21" s="144" t="s">
-        <v>36</v>
+      <c r="I21" s="143">
+        <f t="shared" si="1"/>
+        <v>166</v>
       </c>
-      <c r="J21" s="144">
-        <f>I20-J20</f>
+      <c r="J21" s="143">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K21" s="144">
-        <f>I20-K20</f>
+      <c r="K21" s="143">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L21" s="143">
-        <f>L20-M20</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M21" s="92">
-        <f>IFERROR(L20/M20, 0)</f>
-        <v>0</v>
+      <c r="M21" s="143">
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
-      <c r="N21" s="166">
-        <f>N20-O20</f>
-        <v>0</v>
-      </c>
-      <c r="O21" s="167" t="str">
-        <f>IF(TEXT(N20-O20,"+0,0; -0,0")="+0,0","0,0",TEXT(N20-O20,"+0,0; -0,0"))</f>
-        <v>0,0</v>
-      </c>
-      <c r="P21" s="79"/>
-      <c r="Q21" s="79"/>
-      <c r="R21" s="79"/>
-      <c r="S21" s="79"/>
-      <c r="T21" s="57"/>
-      <c r="U21" s="57"/>
-      <c r="V21" s="57"/>
-      <c r="W21" s="57"/>
-      <c r="X21" s="57"/>
-      <c r="Y21" s="57"/>
-      <c r="Z21" s="57"/>
-      <c r="AA21" s="57"/>
-      <c r="AB21" s="57"/>
-      <c r="AC21" s="57"/>
-      <c r="AD21" s="57"/>
-      <c r="AE21" s="57"/>
-      <c r="AF21" s="57"/>
-      <c r="AG21" s="57"/>
-      <c r="AH21" s="57"/>
-      <c r="AI21" s="57"/>
-      <c r="AJ21" s="57"/>
-      <c r="AK21" s="57"/>
-      <c r="AL21" s="57"/>
-      <c r="AM21" s="57"/>
-      <c r="AN21" s="57"/>
-      <c r="AO21" s="57"/>
-      <c r="AP21" s="57"/>
-      <c r="AQ21" s="57"/>
-      <c r="AR21" s="57"/>
-      <c r="AS21" s="57"/>
-      <c r="AT21" s="57"/>
-      <c r="AU21" s="57"/>
-      <c r="AV21" s="57"/>
-      <c r="AW21" s="57"/>
-      <c r="AX21" s="57"/>
-      <c r="AY21" s="57"/>
-      <c r="AZ21" s="57"/>
-      <c r="BA21" s="57"/>
-      <c r="BB21" s="57"/>
-      <c r="BC21" s="57"/>
-      <c r="BD21" s="57"/>
-      <c r="BE21" s="57"/>
-      <c r="BF21" s="6"/>
-      <c r="BG21" s="6"/>
-      <c r="BH21" s="6"/>
-      <c r="BI21" s="6"/>
-      <c r="BJ21" s="6"/>
-      <c r="BK21" s="6"/>
-      <c r="BL21" s="6"/>
-      <c r="BM21" s="6"/>
-      <c r="BN21" s="6"/>
-      <c r="BO21" s="6"/>
-      <c r="BP21" s="6"/>
-      <c r="BQ21" s="6"/>
-      <c r="BR21" s="6"/>
-      <c r="BS21" s="6"/>
-      <c r="BT21" s="6"/>
-      <c r="BU21" s="6"/>
-      <c r="BV21" s="6"/>
-      <c r="BW21" s="6"/>
-      <c r="BX21" s="6"/>
-      <c r="BY21" s="6"/>
-      <c r="BZ21" s="6"/>
-      <c r="CA21" s="6"/>
-      <c r="CB21" s="6"/>
-      <c r="CC21" s="6"/>
-      <c r="CD21" s="6"/>
-      <c r="CE21" s="57"/>
-      <c r="CF21" s="57"/>
-      <c r="CG21" s="57"/>
-      <c r="CH21" s="57"/>
-      <c r="CI21" s="57"/>
-      <c r="CJ21" s="57"/>
-      <c r="CK21" s="57"/>
-      <c r="CL21" s="57"/>
-      <c r="CM21" s="57"/>
-      <c r="CN21" s="57"/>
-      <c r="CO21" s="57"/>
-      <c r="CP21" s="57"/>
-      <c r="CQ21" s="57"/>
-      <c r="CR21" s="57"/>
-      <c r="CS21" s="57"/>
-      <c r="CT21" s="57"/>
-      <c r="CU21" s="57"/>
-      <c r="CV21" s="57"/>
-      <c r="CW21" s="57"/>
-      <c r="CX21" s="57"/>
-      <c r="CY21" s="57"/>
-      <c r="CZ21" s="57"/>
-      <c r="DA21" s="57"/>
-      <c r="DB21" s="57"/>
-      <c r="DC21" s="57"/>
-      <c r="DD21" s="57"/>
-      <c r="DE21" s="57"/>
-      <c r="DF21" s="78"/>
-    </row>
-    <row r="22" spans="1:211" s="63" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="171" t="s">
-        <v>37</v>
+      <c r="N21" s="91"/>
+      <c r="O21" s="90"/>
+      <c r="P21" s="89"/>
+      <c r="Q21" s="89"/>
+      <c r="R21" s="89"/>
+      <c r="S21" s="89"/>
+      <c r="T21" s="88"/>
+      <c r="U21" s="88"/>
+      <c r="V21" s="88"/>
+      <c r="W21" s="88"/>
+      <c r="X21" s="88"/>
+      <c r="Y21" s="88"/>
+      <c r="Z21" s="86"/>
+      <c r="AA21" s="86"/>
+      <c r="AB21" s="86"/>
+      <c r="AC21" s="86"/>
+      <c r="AD21" s="86"/>
+      <c r="AE21" s="86"/>
+      <c r="AF21" s="86"/>
+      <c r="AG21" s="86"/>
+      <c r="AH21" s="86"/>
+      <c r="AI21" s="86"/>
+      <c r="AJ21" s="86"/>
+      <c r="AK21" s="86"/>
+      <c r="AL21" s="86"/>
+      <c r="AM21" s="86"/>
+      <c r="AN21" s="86"/>
+      <c r="AO21" s="86"/>
+      <c r="AP21" s="86"/>
+      <c r="AQ21" s="86"/>
+      <c r="AR21" s="86"/>
+      <c r="AS21" s="86"/>
+      <c r="AT21" s="86"/>
+      <c r="AU21" s="86"/>
+      <c r="AV21" s="86"/>
+      <c r="AW21" s="86"/>
+      <c r="AX21" s="86"/>
+      <c r="AY21" s="86"/>
+      <c r="AZ21" s="86"/>
+      <c r="BA21" s="86"/>
+      <c r="BB21" s="86"/>
+      <c r="BC21" s="86"/>
+      <c r="BD21" s="86"/>
+      <c r="BE21" s="86"/>
+      <c r="BF21" s="87"/>
+      <c r="BG21" s="87"/>
+      <c r="BH21" s="87"/>
+      <c r="BI21" s="87"/>
+      <c r="BJ21" s="87"/>
+      <c r="BK21" s="87"/>
+      <c r="BL21" s="87"/>
+      <c r="BM21" s="87"/>
+      <c r="BN21" s="87"/>
+      <c r="BO21" s="87"/>
+      <c r="BP21" s="87"/>
+      <c r="BQ21" s="87"/>
+      <c r="BR21" s="87"/>
+      <c r="BS21" s="87"/>
+      <c r="BT21" s="87"/>
+      <c r="BU21" s="87"/>
+      <c r="BV21" s="87"/>
+      <c r="BW21" s="87"/>
+      <c r="BX21" s="87"/>
+      <c r="BY21" s="87"/>
+      <c r="BZ21" s="87"/>
+      <c r="CA21" s="87"/>
+      <c r="CB21" s="87"/>
+      <c r="CC21" s="87"/>
+      <c r="CD21" s="87"/>
+      <c r="CE21" s="86"/>
+      <c r="CF21" s="86"/>
+      <c r="CG21" s="86"/>
+      <c r="CH21" s="86"/>
+      <c r="CI21" s="86"/>
+      <c r="CJ21" s="86"/>
+      <c r="CK21" s="86"/>
+      <c r="CL21" s="86"/>
+      <c r="CM21" s="86"/>
+      <c r="CN21" s="86"/>
+      <c r="CO21" s="86"/>
+      <c r="CP21" s="86"/>
+      <c r="CQ21" s="86"/>
+      <c r="CR21" s="86"/>
+      <c r="CS21" s="86"/>
+      <c r="CT21" s="86"/>
+      <c r="CU21" s="86"/>
+      <c r="CV21" s="86"/>
+      <c r="CW21" s="86"/>
+      <c r="CX21" s="86"/>
+      <c r="CY21" s="86"/>
+      <c r="CZ21" s="86"/>
+      <c r="DA21" s="86"/>
+      <c r="DB21" s="86"/>
+      <c r="DC21" s="86"/>
+      <c r="DD21" s="86"/>
+      <c r="DE21" s="86"/>
+    </row>
+    <row r="22" spans="1:211" s="80" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="145" t="s">
+        <v>34</v>
       </c>
       <c r="B22" s="99">
         <v>1</v>
@@ -8302,7 +8333,7 @@
       <c r="H22" s="100">
         <v>1</v>
       </c>
-      <c r="I22" s="111">
+      <c r="I22" s="77">
         <v>1</v>
       </c>
       <c r="J22" s="101">
@@ -8323,124 +8354,109 @@
       <c r="O22" s="76">
         <v>1</v>
       </c>
-      <c r="P22" s="75"/>
-      <c r="Q22" s="74"/>
-      <c r="R22" s="74"/>
-      <c r="S22" s="65"/>
-      <c r="T22" s="65"/>
-      <c r="U22" s="65"/>
-      <c r="V22" s="65"/>
-      <c r="W22" s="65"/>
-      <c r="X22" s="65"/>
-      <c r="Y22" s="65"/>
-      <c r="Z22" s="65"/>
-      <c r="AA22" s="65"/>
-      <c r="AB22" s="65"/>
-      <c r="AC22" s="65"/>
-      <c r="AD22" s="65"/>
-      <c r="AE22" s="65"/>
-      <c r="AF22" s="65"/>
-      <c r="AG22" s="65"/>
-      <c r="AH22" s="65"/>
-      <c r="AI22" s="65"/>
-      <c r="AJ22" s="65"/>
-      <c r="AK22" s="65"/>
-      <c r="AL22" s="65"/>
-      <c r="AM22" s="65"/>
-      <c r="AN22" s="65"/>
-      <c r="AO22" s="65"/>
-      <c r="AP22" s="65"/>
-      <c r="AQ22" s="65"/>
-      <c r="AR22" s="65"/>
-      <c r="AS22" s="65"/>
-      <c r="AT22" s="65"/>
-      <c r="AU22" s="65"/>
-      <c r="AV22" s="65"/>
-      <c r="AW22" s="65"/>
-      <c r="AX22" s="65"/>
-      <c r="AY22" s="65"/>
-      <c r="AZ22" s="65"/>
-      <c r="BA22" s="65"/>
-      <c r="BB22" s="65"/>
-      <c r="BC22" s="65"/>
-      <c r="BD22" s="65"/>
-      <c r="BE22" s="65"/>
-      <c r="BF22" s="66"/>
-      <c r="BG22" s="66"/>
-      <c r="BH22" s="66"/>
-      <c r="BI22" s="66"/>
-      <c r="BJ22" s="66"/>
-      <c r="BK22" s="66"/>
-      <c r="BL22" s="66"/>
-      <c r="BM22" s="66"/>
-      <c r="BN22" s="66"/>
-      <c r="BO22" s="66"/>
-      <c r="BP22" s="66"/>
-      <c r="BQ22" s="66"/>
-      <c r="BR22" s="66"/>
-      <c r="BS22" s="66"/>
-      <c r="BT22" s="66"/>
-      <c r="BU22" s="66"/>
-      <c r="BV22" s="66"/>
-      <c r="BW22" s="66"/>
-      <c r="BX22" s="66"/>
-      <c r="BY22" s="66"/>
-      <c r="BZ22" s="66"/>
-      <c r="CA22" s="66"/>
-      <c r="CB22" s="66"/>
-      <c r="CC22" s="66"/>
-      <c r="CD22" s="66"/>
-      <c r="CE22" s="65"/>
-      <c r="CF22" s="65"/>
-      <c r="CG22" s="65"/>
-      <c r="CH22" s="65"/>
-      <c r="CI22" s="65"/>
-      <c r="CJ22" s="65"/>
-      <c r="CK22" s="65"/>
-      <c r="CL22" s="65"/>
-      <c r="CM22" s="65"/>
-      <c r="CN22" s="65"/>
-      <c r="CO22" s="65"/>
-      <c r="CP22" s="65"/>
-      <c r="CQ22" s="65"/>
-      <c r="CR22" s="65"/>
-      <c r="CS22" s="65"/>
-      <c r="CT22" s="65"/>
-      <c r="CU22" s="65"/>
-      <c r="CV22" s="65"/>
-      <c r="CW22" s="65"/>
-      <c r="CX22" s="65"/>
-      <c r="CY22" s="65"/>
-      <c r="CZ22" s="65"/>
-      <c r="DA22" s="65"/>
-      <c r="DB22" s="65"/>
-      <c r="DC22" s="65"/>
-      <c r="DD22" s="65"/>
-      <c r="DE22" s="65"/>
-      <c r="DF22" s="64"/>
-      <c r="DI22" s="55"/>
-      <c r="DJ22" s="55"/>
-      <c r="DK22" s="55"/>
-      <c r="DL22" s="55"/>
-      <c r="DM22" s="55"/>
-      <c r="DN22" s="55"/>
-      <c r="DO22" s="55"/>
-      <c r="DP22" s="55"/>
-      <c r="DQ22" s="55"/>
-      <c r="DR22" s="55"/>
-      <c r="DS22" s="55"/>
-      <c r="DT22" s="55"/>
-      <c r="DU22" s="55"/>
-      <c r="DV22" s="55"/>
-      <c r="DW22" s="55"/>
-    </row>
-    <row r="23" spans="1:211" s="55" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="171"/>
+      <c r="P22" s="84"/>
+      <c r="Q22" s="84"/>
+      <c r="R22" s="84"/>
+      <c r="S22" s="84"/>
+      <c r="T22" s="82"/>
+      <c r="U22" s="82"/>
+      <c r="V22" s="82"/>
+      <c r="W22" s="82"/>
+      <c r="X22" s="82"/>
+      <c r="Y22" s="82"/>
+      <c r="Z22" s="82"/>
+      <c r="AA22" s="82"/>
+      <c r="AB22" s="82"/>
+      <c r="AC22" s="82"/>
+      <c r="AD22" s="82"/>
+      <c r="AE22" s="82"/>
+      <c r="AF22" s="82"/>
+      <c r="AG22" s="82"/>
+      <c r="AH22" s="82"/>
+      <c r="AI22" s="82"/>
+      <c r="AJ22" s="82"/>
+      <c r="AK22" s="82"/>
+      <c r="AL22" s="82"/>
+      <c r="AM22" s="82"/>
+      <c r="AN22" s="82"/>
+      <c r="AO22" s="82"/>
+      <c r="AP22" s="82"/>
+      <c r="AQ22" s="82"/>
+      <c r="AR22" s="82"/>
+      <c r="AS22" s="82"/>
+      <c r="AT22" s="82"/>
+      <c r="AU22" s="82"/>
+      <c r="AV22" s="82"/>
+      <c r="AW22" s="82"/>
+      <c r="AX22" s="82"/>
+      <c r="AY22" s="82"/>
+      <c r="AZ22" s="82"/>
+      <c r="BA22" s="82"/>
+      <c r="BB22" s="82"/>
+      <c r="BC22" s="82"/>
+      <c r="BD22" s="82"/>
+      <c r="BE22" s="82"/>
+      <c r="BF22" s="83"/>
+      <c r="BG22" s="83"/>
+      <c r="BH22" s="83"/>
+      <c r="BI22" s="83"/>
+      <c r="BJ22" s="83"/>
+      <c r="BK22" s="83"/>
+      <c r="BL22" s="83"/>
+      <c r="BM22" s="83"/>
+      <c r="BN22" s="83"/>
+      <c r="BO22" s="83"/>
+      <c r="BP22" s="83"/>
+      <c r="BQ22" s="83"/>
+      <c r="BR22" s="83"/>
+      <c r="BS22" s="83"/>
+      <c r="BT22" s="83"/>
+      <c r="BU22" s="83"/>
+      <c r="BV22" s="83"/>
+      <c r="BW22" s="83"/>
+      <c r="BX22" s="83"/>
+      <c r="BY22" s="83"/>
+      <c r="BZ22" s="83"/>
+      <c r="CA22" s="83"/>
+      <c r="CB22" s="83"/>
+      <c r="CC22" s="83"/>
+      <c r="CD22" s="83"/>
+      <c r="CE22" s="82"/>
+      <c r="CF22" s="82"/>
+      <c r="CG22" s="82"/>
+      <c r="CH22" s="82"/>
+      <c r="CI22" s="82"/>
+      <c r="CJ22" s="82"/>
+      <c r="CK22" s="82"/>
+      <c r="CL22" s="82"/>
+      <c r="CM22" s="82"/>
+      <c r="CN22" s="82"/>
+      <c r="CO22" s="82"/>
+      <c r="CP22" s="82"/>
+      <c r="CQ22" s="82"/>
+      <c r="CR22" s="82"/>
+      <c r="CS22" s="82"/>
+      <c r="CT22" s="82"/>
+      <c r="CU22" s="82"/>
+      <c r="CV22" s="82"/>
+      <c r="CW22" s="82"/>
+      <c r="CX22" s="82"/>
+      <c r="CY22" s="82"/>
+      <c r="CZ22" s="82"/>
+      <c r="DA22" s="82"/>
+      <c r="DB22" s="82"/>
+      <c r="DC22" s="82"/>
+      <c r="DD22" s="82"/>
+      <c r="DE22" s="82"/>
+      <c r="FQ22" s="81"/>
+    </row>
+    <row r="23" spans="1:211" s="55" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="145"/>
       <c r="B23" s="143" t="s">
         <v>35</v>
       </c>
       <c r="C23" s="143" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D23" s="143">
         <f>C22-D22</f>
@@ -8451,7 +8467,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="144" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G23" s="144">
         <f>F22-G22</f>
@@ -8462,7 +8478,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="144" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J23" s="144">
         <f>I22-J22</f>
@@ -8480,18 +8496,18 @@
         <f>IFERROR(L22/M22, 0)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="166">
+      <c r="N23" s="146">
         <f>N22-O22</f>
         <v>0</v>
       </c>
-      <c r="O23" s="167" t="str">
+      <c r="O23" s="147" t="str">
         <f>IF(TEXT(N22-O22,"+0,0; -0,0")="+0,0","0,0",TEXT(N22-O22,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
-      <c r="P23" s="57"/>
-      <c r="Q23" s="56"/>
-      <c r="R23" s="56"/>
-      <c r="S23" s="56"/>
+      <c r="P23" s="79"/>
+      <c r="Q23" s="79"/>
+      <c r="R23" s="79"/>
+      <c r="S23" s="79"/>
       <c r="T23" s="57"/>
       <c r="U23" s="57"/>
       <c r="V23" s="57"/>
@@ -8582,7 +8598,7 @@
       <c r="DC23" s="57"/>
       <c r="DD23" s="57"/>
       <c r="DE23" s="57"/>
-      <c r="DF23" s="56"/>
+      <c r="DF23" s="78"/>
     </row>
     <row r="24" spans="1:211" s="55" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="61"/>
@@ -8706,19 +8722,19 @@
     <row r="25" spans="1:211" s="55" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="67"/>
       <c r="B25" s="67"/>
-      <c r="C25" s="146" t="s">
+      <c r="C25" s="153" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="147"/>
-      <c r="E25" s="147"/>
-      <c r="F25" s="147"/>
+      <c r="D25" s="154"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="154"/>
       <c r="G25" s="67"/>
       <c r="H25" s="67"/>
       <c r="I25" s="67"/>
       <c r="J25" s="67"/>
-      <c r="K25" s="145"/>
-      <c r="L25" s="145"/>
-      <c r="M25" s="145"/>
+      <c r="K25" s="152"/>
+      <c r="L25" s="152"/>
+      <c r="M25" s="152"/>
       <c r="N25" s="67"/>
       <c r="O25" s="67"/>
       <c r="P25" s="67"/>
@@ -8919,21 +8935,21 @@
       <c r="HC25" s="62"/>
     </row>
     <row r="26" spans="1:211" s="55" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="145"/>
-      <c r="B26" s="145"/>
-      <c r="C26" s="145"/>
-      <c r="D26" s="145"/>
-      <c r="E26" s="145"/>
-      <c r="F26" s="145"/>
-      <c r="G26" s="145"/>
-      <c r="H26" s="145"/>
-      <c r="I26" s="145"/>
-      <c r="J26" s="145"/>
-      <c r="K26" s="145"/>
-      <c r="L26" s="145"/>
-      <c r="M26" s="145"/>
-      <c r="N26" s="145"/>
-      <c r="O26" s="145"/>
+      <c r="A26" s="152"/>
+      <c r="B26" s="152"/>
+      <c r="C26" s="152"/>
+      <c r="D26" s="152"/>
+      <c r="E26" s="152"/>
+      <c r="F26" s="152"/>
+      <c r="G26" s="152"/>
+      <c r="H26" s="152"/>
+      <c r="I26" s="152"/>
+      <c r="J26" s="152"/>
+      <c r="K26" s="152"/>
+      <c r="L26" s="152"/>
+      <c r="M26" s="152"/>
+      <c r="N26" s="152"/>
+      <c r="O26" s="152"/>
       <c r="P26" s="58"/>
       <c r="Q26" s="58"/>
       <c r="R26" s="58"/>
@@ -57536,24 +57552,9 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="N17:O17"/>
     <mergeCell ref="A16:A17"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="A18:A19"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="N9:O9"/>
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="K25:M25"/>
@@ -57570,6 +57571,21 @@
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="N23:O23"/>
   </mergeCells>
   <phoneticPr fontId="59" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/internal/lib/service/excel/templates/res-summary.xlsx
+++ b/internal/lib/service/excel/templates/res-summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\go\srmt-prime\internal\lib\service\excel\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A065FCBA-07D4-42FC-831C-F35911AFA5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149D9512-A7C5-481C-858B-10199DD5FEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27840" yWindow="960" windowWidth="21600" windowHeight="11235" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="16.12 (P)" sheetId="1" r:id="rId1"/>
@@ -1702,7 +1702,7 @@
     <xf numFmtId="166" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2204,32 +2204,28 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="173" fontId="19" fillId="15" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="19" fillId="16" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="173" fontId="19" fillId="15" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="15" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="16" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="35" fillId="12" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2306,24 +2302,32 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="19" fillId="15" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="35" fillId="12" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="173" fontId="19" fillId="16" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="15" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="16" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="9" fontId="19" fillId="8" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2386,7 +2390,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAA4wJ+AA8AAAAAAAAAHgOSAF8BAADDJgAAOAAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAA4wJ+AA8AAAAAAAAAHgOSAF8BAADDJgAAOAAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2462,7 +2466,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAWAOGAAUAAAAAAAAAkwOaAHYBAAAADwAAOAAAADMAAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAWAOGAAUAAAAAAAAAkwOaAHYBAAAADwAAOAAAADMAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2538,7 +2542,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAA5wKIAAsAAAAAAAAAIgObAHsBAAArHQAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAA5wKIAAsAAAAAAAAAIgObAHsBAAArHQAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2614,7 +2618,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAbgKHAAUAAAAAAAAAqAKaAHkBAAA4DgAANQAAADIAAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAbgKHAAUAAAAAAAAAqAKaAHkBAAA4DgAANQAAADIAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2690,7 +2694,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAAUgDdAAYAAAAAAAAAywDwAGgCAACyDwAANQAAADIAAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAAUgDdAAYAAAAAAAAAywDwAGgCAACyDwAANQAAADIAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2766,7 +2770,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAA5AKDAAcAAAAAAAAAHgOXAG0BAACMEwAAOAAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAA5AKDAAcAAAAAAAAAHgOXAG0BAACMEwAAOAAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2842,7 +2846,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAAxAOCAAcAAAAAAAAA/wOVAGsBAABBFAAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAAxAOCAAcAAAAAAAAA/wOVAGsBAABBFAAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2918,7 +2922,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAgAAAAAAAAATgG1AAgAAAAAAAAAxQHIAPkBAAD1FAAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAgAAAAAAAAATgG1AAgAAAAAAAAAxQHIAPkBAAD1FAAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2994,7 +2998,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAkAAAAAAAAATQODAAkAAAAAAAAAiQOWAG0BAACvGAAANQAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAkAAAAAAAAATQODAAkAAAAAAAAAiQOWAG0BAACvGAAANQAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3070,7 +3074,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAoAAAAAAAAAfACCAAoAAAAAAAAA+ACVAGsBAABwGQAANQAAADEAAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAoAAAAAAAAAfACCAAoAAAAAAAAA+ACVAGsBAABwGQAANQAAADEAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3146,7 +3150,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAAywODAA4AAAAAAAAACACWAG0BAACwIgAANQAAAC4AAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAAywODAA4AAAAAAAAACACWAG0BAACwIgAANQAAAC4AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3222,7 +3226,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA4AAAAAAAAAOgG1AA4AAAAAAAAAsAHIAPkBAABXIwAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA4AAAAAAAAAOgG1AA4AAAAAAAAAsAHIAPkBAABXIwAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3298,7 +3302,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAI8MAQAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAAxwOBAA8AAAAAAAAAAASUAGgBAAB7JwAANQAAAC4AAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAI8MAQAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAAxwOBAA8AAAAAAAAAAASUAGgBAAB7JwAANQAAAC4AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3374,7 +3378,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAABAAAAAAAAAAXQGxABAAAAAAAAAA1AHFAO4BAAAzKAAANwAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAABAAAAAAAAAAXQGxABAAAAAAAAAA1AHFAO4BAAAzKAAANwAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3450,7 +3454,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAAvgOHAAsAAAAAAAAA+QObAHkBAADYHQAANwAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAAvgOHAAsAAAAAAAAA+QObAHkBAADYHQAANwAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3526,7 +3530,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAwAAAAAAAAAPAG9AAwAAAAAAAAAtQHQAA8CAACKHgAANQAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAwAAAAAAAAAPAG9AAwAAAAAAAAAtQHQAA8CAACKHgAANQAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3602,7 +3606,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAA6gKAAA0AAAAAAAAAJgOUAGUBAAD7IQAAOAAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAA6gKAAA0AAAAAAAAAJgOUAGUBAAD7IQAAOAAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3678,7 +3682,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAADgLfAAYAAAAAAAAAhQLyAG4CAABqEAAANQAAADEAAAAAAAAA"/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAADgLfAAYAAAAAAAAAhQLyAG4CAABqEAAANQAAADEAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -4016,23 +4020,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:204" ht="29.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
-      <c r="L1" s="155"/>
-      <c r="M1" s="155"/>
-      <c r="N1" s="155"/>
-      <c r="O1" s="155"/>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154"/>
+      <c r="G1" s="154"/>
+      <c r="H1" s="154"/>
+      <c r="I1" s="154"/>
+      <c r="J1" s="154"/>
+      <c r="K1" s="154"/>
+      <c r="L1" s="154"/>
+      <c r="M1" s="154"/>
+      <c r="N1" s="154"/>
+      <c r="O1" s="154"/>
       <c r="P1" s="132"/>
       <c r="Q1" s="132"/>
       <c r="R1" s="132"/>
@@ -4148,12 +4152,12 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
-      <c r="L2" s="156">
+      <c r="L2" s="155">
         <v>46007</v>
       </c>
-      <c r="M2" s="156"/>
-      <c r="N2" s="156"/>
-      <c r="O2" s="156"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="155"/>
       <c r="P2" s="130"/>
       <c r="Q2" s="129"/>
       <c r="R2" s="129"/>
@@ -4254,35 +4258,35 @@
       <c r="FZ2" s="123"/>
     </row>
     <row r="3" spans="1:204" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="163" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="140" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="157" t="s">
+      <c r="C3" s="156" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="157" t="s">
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="156" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="158"/>
-      <c r="H3" s="159"/>
-      <c r="I3" s="157" t="s">
+      <c r="G3" s="157"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="156" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="160" t="s">
+      <c r="J3" s="157"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="161"/>
-      <c r="N3" s="160" t="s">
+      <c r="M3" s="160"/>
+      <c r="N3" s="159" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="161"/>
+      <c r="O3" s="160"/>
       <c r="P3" s="24"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
@@ -4380,39 +4384,39 @@
       <c r="FS3" s="123"/>
     </row>
     <row r="4" spans="1:204" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="165"/>
-      <c r="B4" s="169">
+      <c r="A4" s="164"/>
+      <c r="B4" s="168">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="C4" s="151">
+      <c r="C4" s="170">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="165" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="167"/>
+      <c r="E4" s="166"/>
       <c r="F4" s="139">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="G4" s="166" t="s">
+      <c r="G4" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="167"/>
-      <c r="I4" s="151">
+      <c r="H4" s="166"/>
+      <c r="I4" s="170">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="J4" s="166" t="s">
+      <c r="J4" s="165" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="168"/>
-      <c r="L4" s="162"/>
-      <c r="M4" s="163"/>
-      <c r="N4" s="162"/>
-      <c r="O4" s="163"/>
+      <c r="K4" s="167"/>
+      <c r="L4" s="161"/>
+      <c r="M4" s="162"/>
+      <c r="N4" s="161"/>
+      <c r="O4" s="162"/>
       <c r="P4" s="121"/>
       <c r="Q4" s="121"/>
       <c r="R4" s="121"/>
@@ -4509,9 +4513,9 @@
       <c r="DE4" s="4"/>
     </row>
     <row r="5" spans="1:204" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="165"/>
-      <c r="B5" s="170"/>
-      <c r="C5" s="151"/>
+      <c r="A5" s="164"/>
+      <c r="B5" s="169"/>
+      <c r="C5" s="170"/>
       <c r="D5" s="136">
         <f>YEAR($L$2)-1</f>
         <v>2024</v>
@@ -4531,7 +4535,7 @@
         <f>YEAR($L$2)-2</f>
         <v>2023</v>
       </c>
-      <c r="I5" s="151"/>
+      <c r="I5" s="170"/>
       <c r="J5" s="136">
         <f>YEAR($L$2)-1</f>
         <v>2024</v>
@@ -4747,7 +4751,7 @@
       <c r="GV5" s="117"/>
     </row>
     <row r="6" spans="1:204" s="93" customFormat="1" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="148" t="s">
+      <c r="A6" s="171" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="99">
@@ -4983,7 +4987,7 @@
       <c r="GV6" s="106"/>
     </row>
     <row r="7" spans="1:204" ht="21.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="148"/>
+      <c r="A7" s="171"/>
       <c r="B7" s="143" t="s">
         <v>12</v>
       </c>
@@ -5028,11 +5032,11 @@
         <f>IFERROR(L6/M6, 0)</f>
         <v>1</v>
       </c>
-      <c r="N7" s="146">
+      <c r="N7" s="145">
         <f>N6-O6</f>
         <v>0</v>
       </c>
-      <c r="O7" s="147" t="str">
+      <c r="O7" s="172" t="str">
         <f>IF(TEXT(N6-O6,"+0,0; -0,0")="+0,0","0,0",TEXT(N6-O6,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -5227,7 +5231,7 @@
       <c r="GV7" s="113"/>
     </row>
     <row r="8" spans="1:204" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="148" t="s">
+      <c r="A8" s="171" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="99">
@@ -5463,7 +5467,7 @@
       <c r="GV8" s="106"/>
     </row>
     <row r="9" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="148"/>
+      <c r="A9" s="171"/>
       <c r="B9" s="143" t="s">
         <v>16</v>
       </c>
@@ -5508,11 +5512,11 @@
         <f>IFERROR(L8/M8, 0)</f>
         <v>1</v>
       </c>
-      <c r="N9" s="146">
+      <c r="N9" s="145">
         <f>N8-O8</f>
         <v>0</v>
       </c>
-      <c r="O9" s="147" t="str">
+      <c r="O9" s="172" t="str">
         <f>IF(TEXT(N8-O8,"+0,0; -0,0")="+0,0","0,0",TEXT(N8-O8,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -5707,7 +5711,7 @@
       <c r="GV9" s="102"/>
     </row>
     <row r="10" spans="1:204" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="148" t="s">
+      <c r="A10" s="171" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="99">
@@ -5939,7 +5943,7 @@
       <c r="GV10" s="106"/>
     </row>
     <row r="11" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="148"/>
+      <c r="A11" s="171"/>
       <c r="B11" s="143" t="s">
         <v>20</v>
       </c>
@@ -5984,8 +5988,8 @@
         <f>IFERROR(L10/M10, 0)</f>
         <v>1</v>
       </c>
-      <c r="N11" s="149"/>
-      <c r="O11" s="150"/>
+      <c r="N11" s="173"/>
+      <c r="O11" s="174"/>
       <c r="P11" s="89"/>
       <c r="Q11" s="89"/>
       <c r="R11" s="109"/>
@@ -6177,7 +6181,7 @@
       <c r="GV11" s="102"/>
     </row>
     <row r="12" spans="1:204" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="148" t="s">
+      <c r="A12" s="171" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="99">
@@ -6413,7 +6417,7 @@
       <c r="GV12" s="106"/>
     </row>
     <row r="13" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="148"/>
+      <c r="A13" s="171"/>
       <c r="B13" s="143" t="s">
         <v>23</v>
       </c>
@@ -6458,11 +6462,11 @@
         <f>IFERROR(L12/M12, 0)</f>
         <v>1</v>
       </c>
-      <c r="N13" s="146">
+      <c r="N13" s="145">
         <f>N12-O12</f>
         <v>0</v>
       </c>
-      <c r="O13" s="147" t="str">
+      <c r="O13" s="172" t="str">
         <f>IF(TEXT(N12-O12,"+0,0; -0,0")="+0,0","0,0",TEXT(N12-O12,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -6657,7 +6661,7 @@
       <c r="GV13" s="102"/>
     </row>
     <row r="14" spans="1:204" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="148" t="s">
+      <c r="A14" s="171" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="99">
@@ -6893,7 +6897,7 @@
       <c r="GV14" s="106"/>
     </row>
     <row r="15" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="148"/>
+      <c r="A15" s="171"/>
       <c r="B15" s="143" t="s">
         <v>25</v>
       </c>
@@ -6938,11 +6942,11 @@
         <f>IFERROR(L14/M14, 0)</f>
         <v>1</v>
       </c>
-      <c r="N15" s="146">
+      <c r="N15" s="145">
         <f>N14-O14</f>
         <v>0</v>
       </c>
-      <c r="O15" s="147" t="str">
+      <c r="O15" s="172" t="str">
         <f>IF(TEXT(N14-O14,"+0,0; -0,0")="+0,0","0,0",TEXT(N14-O14,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -7137,7 +7141,7 @@
       <c r="GV15" s="102"/>
     </row>
     <row r="16" spans="1:204" s="105" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="172" t="s">
+      <c r="A16" s="147" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="99">
@@ -7373,7 +7377,7 @@
       <c r="GV16" s="106"/>
     </row>
     <row r="17" spans="1:211" s="85" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="173"/>
+      <c r="A17" s="148"/>
       <c r="B17" s="143" t="s">
         <v>29</v>
       </c>
@@ -7418,11 +7422,11 @@
         <f>IFERROR(L16/M16, 0)</f>
         <v>1</v>
       </c>
-      <c r="N17" s="146">
+      <c r="N17" s="145">
         <f>N16-O16</f>
         <v>0</v>
       </c>
-      <c r="O17" s="171" t="str">
+      <c r="O17" s="146" t="str">
         <f>IF(TEXT(N16-O16,"+0,0; -0,0")="+0,0","0,0",TEXT(N16-O16,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -7617,7 +7621,7 @@
       <c r="GV17" s="102"/>
     </row>
     <row r="18" spans="1:211" s="63" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="145" t="s">
+      <c r="A18" s="175" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="99">
@@ -7774,7 +7778,7 @@
       <c r="DW18" s="55"/>
     </row>
     <row r="19" spans="1:211" s="55" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="145"/>
+      <c r="A19" s="175"/>
       <c r="B19" s="143" t="s">
         <v>35</v>
       </c>
@@ -7819,11 +7823,11 @@
         <f>IFERROR(L18/M18, 0)</f>
         <v>0</v>
       </c>
-      <c r="N19" s="146">
+      <c r="N19" s="145">
         <f>N18-O18</f>
         <v>0</v>
       </c>
-      <c r="O19" s="147" t="str">
+      <c r="O19" s="172" t="str">
         <f>IF(TEXT(N18-O18,"+0,0; -0,0")="+0,0","0,0",TEXT(N18-O18,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -7924,7 +7928,7 @@
       <c r="DF19" s="56"/>
     </row>
     <row r="20" spans="1:211" s="93" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="174" t="s">
+      <c r="A20" s="149" t="s">
         <v>33</v>
       </c>
       <c r="B20" s="99"/>
@@ -8165,51 +8169,51 @@
       <c r="GV20" s="94"/>
     </row>
     <row r="21" spans="1:211" s="85" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="175"/>
+      <c r="A21" s="150"/>
       <c r="B21" s="143"/>
-      <c r="C21" s="143">
+      <c r="C21" s="176">
         <f>C7+C9+C11+C13+C15+C17+C19</f>
         <v>-6.5299999999999994</v>
       </c>
-      <c r="D21" s="143">
+      <c r="D21" s="176">
         <f t="shared" ref="D21:M21" si="1">D7+D9+D11+D13+D15+D17+D19</f>
         <v>0</v>
       </c>
-      <c r="E21" s="143">
+      <c r="E21" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F21" s="143">
+      <c r="F21" s="176">
         <f t="shared" si="1"/>
         <v>-27.14</v>
       </c>
-      <c r="G21" s="143">
+      <c r="G21" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H21" s="143">
+      <c r="H21" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I21" s="143">
+      <c r="I21" s="176">
         <f t="shared" si="1"/>
         <v>166</v>
       </c>
-      <c r="J21" s="143">
+      <c r="J21" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K21" s="143">
+      <c r="K21" s="176">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="L21" s="143">
+      <c r="L21" s="176">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M21" s="143">
-        <f t="shared" si="1"/>
-        <v>6</v>
+      <c r="M21" s="92">
+        <f>IFERROR(L20/M20, 0)</f>
+        <v>1</v>
       </c>
       <c r="N21" s="91"/>
       <c r="O21" s="90"/>
@@ -8309,7 +8313,7 @@
       <c r="DE21" s="86"/>
     </row>
     <row r="22" spans="1:211" s="80" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="145" t="s">
+      <c r="A22" s="175" t="s">
         <v>34</v>
       </c>
       <c r="B22" s="99">
@@ -8451,7 +8455,7 @@
       <c r="FQ22" s="81"/>
     </row>
     <row r="23" spans="1:211" s="55" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="145"/>
+      <c r="A23" s="175"/>
       <c r="B23" s="143" t="s">
         <v>35</v>
       </c>
@@ -8496,11 +8500,11 @@
         <f>IFERROR(L22/M22, 0)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="146">
+      <c r="N23" s="145">
         <f>N22-O22</f>
         <v>0</v>
       </c>
-      <c r="O23" s="147" t="str">
+      <c r="O23" s="172" t="str">
         <f>IF(TEXT(N22-O22,"+0,0; -0,0")="+0,0","0,0",TEXT(N22-O22,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -8722,19 +8726,19 @@
     <row r="25" spans="1:211" s="55" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="67"/>
       <c r="B25" s="67"/>
-      <c r="C25" s="153" t="s">
+      <c r="C25" s="152" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="154"/>
-      <c r="E25" s="154"/>
-      <c r="F25" s="154"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="153"/>
       <c r="G25" s="67"/>
       <c r="H25" s="67"/>
       <c r="I25" s="67"/>
       <c r="J25" s="67"/>
-      <c r="K25" s="152"/>
-      <c r="L25" s="152"/>
-      <c r="M25" s="152"/>
+      <c r="K25" s="151"/>
+      <c r="L25" s="151"/>
+      <c r="M25" s="151"/>
       <c r="N25" s="67"/>
       <c r="O25" s="67"/>
       <c r="P25" s="67"/>
@@ -8935,21 +8939,21 @@
       <c r="HC25" s="62"/>
     </row>
     <row r="26" spans="1:211" s="55" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="152"/>
-      <c r="B26" s="152"/>
-      <c r="C26" s="152"/>
-      <c r="D26" s="152"/>
-      <c r="E26" s="152"/>
-      <c r="F26" s="152"/>
-      <c r="G26" s="152"/>
-      <c r="H26" s="152"/>
-      <c r="I26" s="152"/>
-      <c r="J26" s="152"/>
-      <c r="K26" s="152"/>
-      <c r="L26" s="152"/>
-      <c r="M26" s="152"/>
-      <c r="N26" s="152"/>
-      <c r="O26" s="152"/>
+      <c r="A26" s="151"/>
+      <c r="B26" s="151"/>
+      <c r="C26" s="151"/>
+      <c r="D26" s="151"/>
+      <c r="E26" s="151"/>
+      <c r="F26" s="151"/>
+      <c r="G26" s="151"/>
+      <c r="H26" s="151"/>
+      <c r="I26" s="151"/>
+      <c r="J26" s="151"/>
+      <c r="K26" s="151"/>
+      <c r="L26" s="151"/>
+      <c r="M26" s="151"/>
+      <c r="N26" s="151"/>
+      <c r="O26" s="151"/>
       <c r="P26" s="58"/>
       <c r="Q26" s="58"/>
       <c r="R26" s="58"/>
@@ -57552,12 +57556,18 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A26:O26"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="N11:O11"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="C3:E3"/>
@@ -57572,18 +57582,12 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="I4:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A26:O26"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="K25:M25"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="N23:O23"/>
   </mergeCells>

--- a/internal/lib/service/excel/templates/res-summary.xlsx
+++ b/internal/lib/service/excel/templates/res-summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\go\srmt-prime\internal\lib\service\excel\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149D9512-A7C5-481C-858B-10199DD5FEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D2CBEC-9ED4-45C6-9A57-3532BE190248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27840" yWindow="960" windowWidth="21600" windowHeight="11235" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="16.12 (P)" sheetId="1" r:id="rId1"/>
@@ -1702,7 +1702,7 @@
     <xf numFmtId="166" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2204,40 +2204,29 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="173" fontId="19" fillId="15" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="19" fillId="15" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="173" fontId="19" fillId="16" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="19" fillId="15" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="19" fillId="16" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2306,27 +2295,42 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="173" fontId="19" fillId="15" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="19" fillId="16" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="15" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="16" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="8" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="19" fillId="8" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2390,7 +2394,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAA4wJ+AA8AAAAAAAAAHgOSAF8BAADDJgAAOAAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAA4wJ+AA8AAAAAAAAAHgOSAF8BAADDJgAAOAAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2466,7 +2470,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAWAOGAAUAAAAAAAAAkwOaAHYBAAAADwAAOAAAADMAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAWAOGAAUAAAAAAAAAkwOaAHYBAAAADwAAOAAAADMAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2542,7 +2546,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAA5wKIAAsAAAAAAAAAIgObAHsBAAArHQAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAA5wKIAAsAAAAAAAAAIgObAHsBAAArHQAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2618,7 +2622,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAbgKHAAUAAAAAAAAAqAKaAHkBAAA4DgAANQAAADIAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAbgKHAAUAAAAAAAAAqAKaAHkBAAA4DgAANQAAADIAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2694,7 +2698,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAAUgDdAAYAAAAAAAAAywDwAGgCAACyDwAANQAAADIAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAAUgDdAAYAAAAAAAAAywDwAGgCAACyDwAANQAAADIAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2770,7 +2774,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAA5AKDAAcAAAAAAAAAHgOXAG0BAACMEwAAOAAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAA5AKDAAcAAAAAAAAAHgOXAG0BAACMEwAAOAAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2846,7 +2850,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAAxAOCAAcAAAAAAAAA/wOVAGsBAABBFAAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAAxAOCAAcAAAAAAAAA/wOVAGsBAABBFAAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2922,7 +2926,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAgAAAAAAAAATgG1AAgAAAAAAAAAxQHIAPkBAAD1FAAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAgAAAAAAAAATgG1AAgAAAAAAAAAxQHIAPkBAAD1FAAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2998,7 +3002,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAkAAAAAAAAATQODAAkAAAAAAAAAiQOWAG0BAACvGAAANQAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAkAAAAAAAAATQODAAkAAAAAAAAAiQOWAG0BAACvGAAANQAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3074,7 +3078,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAoAAAAAAAAAfACCAAoAAAAAAAAA+ACVAGsBAABwGQAANQAAADEAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAoAAAAAAAAAfACCAAoAAAAAAAAA+ACVAGsBAABwGQAANQAAADEAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3150,7 +3154,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAAywODAA4AAAAAAAAACACWAG0BAACwIgAANQAAAC4AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAAywODAA4AAAAAAAAACACWAG0BAACwIgAANQAAAC4AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3226,7 +3230,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA4AAAAAAAAAOgG1AA4AAAAAAAAAsAHIAPkBAABXIwAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA4AAAAAAAAAOgG1AA4AAAAAAAAAsAHIAPkBAABXIwAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3302,7 +3306,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAI8MAQAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAAxwOBAA8AAAAAAAAAAASUAGgBAAB7JwAANQAAAC4AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAI8MAQAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAAxwOBAA8AAAAAAAAAAASUAGgBAAB7JwAANQAAAC4AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3378,7 +3382,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAABAAAAAAAAAAXQGxABAAAAAAAAAA1AHFAO4BAAAzKAAANwAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAABAAAAAAAAAAXQGxABAAAAAAAAAA1AHFAO4BAAAzKAAANwAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3454,7 +3458,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAAvgOHAAsAAAAAAAAA+QObAHkBAADYHQAANwAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAAvgOHAAsAAAAAAAAA+QObAHkBAADYHQAANwAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3530,7 +3534,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAwAAAAAAAAAPAG9AAwAAAAAAAAAtQHQAA8CAACKHgAANQAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAwAAAAAAAAAPAG9AAwAAAAAAAAAtQHQAA8CAACKHgAANQAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3606,7 +3610,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAA6gKAAA0AAAAAAAAAJgOUAGUBAAD7IQAAOAAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAA6gKAAA0AAAAAAAAAJgOUAGUBAAD7IQAAOAAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3682,7 +3686,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAADgLfAAYAAAAAAAAAhQLyAG4CAABqEAAANQAAADEAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAADgLfAAYAAAAAAAAAhQLyAG4CAABqEAAANQAAADEAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -4020,23 +4024,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:204" ht="29.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
-      <c r="L1" s="154"/>
-      <c r="M1" s="154"/>
-      <c r="N1" s="154"/>
-      <c r="O1" s="154"/>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
       <c r="P1" s="132"/>
       <c r="Q1" s="132"/>
       <c r="R1" s="132"/>
@@ -4152,12 +4156,12 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
-      <c r="L2" s="155">
+      <c r="L2" s="152">
         <v>46007</v>
       </c>
-      <c r="M2" s="155"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="155"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="152"/>
       <c r="P2" s="130"/>
       <c r="Q2" s="129"/>
       <c r="R2" s="129"/>
@@ -4258,35 +4262,35 @@
       <c r="FZ2" s="123"/>
     </row>
     <row r="3" spans="1:204" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="163" t="s">
+      <c r="A3" s="160" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="140" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="156" t="s">
+      <c r="C3" s="153" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="156" t="s">
+      <c r="D3" s="154"/>
+      <c r="E3" s="154"/>
+      <c r="F3" s="153" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="157"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="156" t="s">
+      <c r="G3" s="154"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="153" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="157"/>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159" t="s">
+      <c r="J3" s="154"/>
+      <c r="K3" s="155"/>
+      <c r="L3" s="156" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="160"/>
-      <c r="N3" s="159" t="s">
+      <c r="M3" s="157"/>
+      <c r="N3" s="156" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="160"/>
+      <c r="O3" s="157"/>
       <c r="P3" s="24"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
@@ -4384,39 +4388,39 @@
       <c r="FS3" s="123"/>
     </row>
     <row r="4" spans="1:204" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="164"/>
-      <c r="B4" s="168">
+      <c r="A4" s="161"/>
+      <c r="B4" s="165">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="C4" s="170">
+      <c r="C4" s="167">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="D4" s="165" t="s">
+      <c r="D4" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="166"/>
+      <c r="E4" s="163"/>
       <c r="F4" s="139">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="G4" s="165" t="s">
+      <c r="G4" s="162" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="166"/>
-      <c r="I4" s="170">
+      <c r="H4" s="163"/>
+      <c r="I4" s="167">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="J4" s="165" t="s">
+      <c r="J4" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="167"/>
-      <c r="L4" s="161"/>
-      <c r="M4" s="162"/>
-      <c r="N4" s="161"/>
-      <c r="O4" s="162"/>
+      <c r="K4" s="164"/>
+      <c r="L4" s="158"/>
+      <c r="M4" s="159"/>
+      <c r="N4" s="158"/>
+      <c r="O4" s="159"/>
       <c r="P4" s="121"/>
       <c r="Q4" s="121"/>
       <c r="R4" s="121"/>
@@ -4513,9 +4517,9 @@
       <c r="DE4" s="4"/>
     </row>
     <row r="5" spans="1:204" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="164"/>
-      <c r="B5" s="169"/>
-      <c r="C5" s="170"/>
+      <c r="A5" s="161"/>
+      <c r="B5" s="166"/>
+      <c r="C5" s="167"/>
       <c r="D5" s="136">
         <f>YEAR($L$2)-1</f>
         <v>2024</v>
@@ -4535,7 +4539,7 @@
         <f>YEAR($L$2)-2</f>
         <v>2023</v>
       </c>
-      <c r="I5" s="170"/>
+      <c r="I5" s="167"/>
       <c r="J5" s="136">
         <f>YEAR($L$2)-1</f>
         <v>2024</v>
@@ -4751,7 +4755,7 @@
       <c r="GV5" s="117"/>
     </row>
     <row r="6" spans="1:204" s="93" customFormat="1" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="171" t="s">
+      <c r="A6" s="145" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="99">
@@ -4987,7 +4991,7 @@
       <c r="GV6" s="106"/>
     </row>
     <row r="7" spans="1:204" ht="21.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="171"/>
+      <c r="A7" s="145"/>
       <c r="B7" s="143" t="s">
         <v>12</v>
       </c>
@@ -5032,11 +5036,11 @@
         <f>IFERROR(L6/M6, 0)</f>
         <v>1</v>
       </c>
-      <c r="N7" s="145">
+      <c r="N7" s="146">
         <f>N6-O6</f>
         <v>0</v>
       </c>
-      <c r="O7" s="172" t="str">
+      <c r="O7" s="147" t="str">
         <f>IF(TEXT(N6-O6,"+0,0; -0,0")="+0,0","0,0",TEXT(N6-O6,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -5231,7 +5235,7 @@
       <c r="GV7" s="113"/>
     </row>
     <row r="8" spans="1:204" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="171" t="s">
+      <c r="A8" s="145" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="99">
@@ -5467,7 +5471,7 @@
       <c r="GV8" s="106"/>
     </row>
     <row r="9" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="171"/>
+      <c r="A9" s="145"/>
       <c r="B9" s="143" t="s">
         <v>16</v>
       </c>
@@ -5512,11 +5516,11 @@
         <f>IFERROR(L8/M8, 0)</f>
         <v>1</v>
       </c>
-      <c r="N9" s="145">
+      <c r="N9" s="146">
         <f>N8-O8</f>
         <v>0</v>
       </c>
-      <c r="O9" s="172" t="str">
+      <c r="O9" s="147" t="str">
         <f>IF(TEXT(N8-O8,"+0,0; -0,0")="+0,0","0,0",TEXT(N8-O8,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -5711,7 +5715,7 @@
       <c r="GV9" s="102"/>
     </row>
     <row r="10" spans="1:204" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="171" t="s">
+      <c r="A10" s="145" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="99">
@@ -5943,7 +5947,7 @@
       <c r="GV10" s="106"/>
     </row>
     <row r="11" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="171"/>
+      <c r="A11" s="145"/>
       <c r="B11" s="143" t="s">
         <v>20</v>
       </c>
@@ -5988,8 +5992,8 @@
         <f>IFERROR(L10/M10, 0)</f>
         <v>1</v>
       </c>
-      <c r="N11" s="173"/>
-      <c r="O11" s="174"/>
+      <c r="N11" s="149"/>
+      <c r="O11" s="150"/>
       <c r="P11" s="89"/>
       <c r="Q11" s="89"/>
       <c r="R11" s="109"/>
@@ -6181,7 +6185,7 @@
       <c r="GV11" s="102"/>
     </row>
     <row r="12" spans="1:204" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="171" t="s">
+      <c r="A12" s="145" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="99">
@@ -6417,7 +6421,7 @@
       <c r="GV12" s="106"/>
     </row>
     <row r="13" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="171"/>
+      <c r="A13" s="145"/>
       <c r="B13" s="143" t="s">
         <v>23</v>
       </c>
@@ -6462,11 +6466,11 @@
         <f>IFERROR(L12/M12, 0)</f>
         <v>1</v>
       </c>
-      <c r="N13" s="145">
+      <c r="N13" s="146">
         <f>N12-O12</f>
         <v>0</v>
       </c>
-      <c r="O13" s="172" t="str">
+      <c r="O13" s="147" t="str">
         <f>IF(TEXT(N12-O12,"+0,0; -0,0")="+0,0","0,0",TEXT(N12-O12,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -6661,7 +6665,7 @@
       <c r="GV13" s="102"/>
     </row>
     <row r="14" spans="1:204" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="171" t="s">
+      <c r="A14" s="145" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="99">
@@ -6897,7 +6901,7 @@
       <c r="GV14" s="106"/>
     </row>
     <row r="15" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="171"/>
+      <c r="A15" s="145"/>
       <c r="B15" s="143" t="s">
         <v>25</v>
       </c>
@@ -6942,11 +6946,11 @@
         <f>IFERROR(L14/M14, 0)</f>
         <v>1</v>
       </c>
-      <c r="N15" s="145">
+      <c r="N15" s="146">
         <f>N14-O14</f>
         <v>0</v>
       </c>
-      <c r="O15" s="172" t="str">
+      <c r="O15" s="147" t="str">
         <f>IF(TEXT(N14-O14,"+0,0; -0,0")="+0,0","0,0",TEXT(N14-O14,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -7141,7 +7145,7 @@
       <c r="GV15" s="102"/>
     </row>
     <row r="16" spans="1:204" s="105" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="147" t="s">
+      <c r="A16" s="169" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="99">
@@ -7377,7 +7381,7 @@
       <c r="GV16" s="106"/>
     </row>
     <row r="17" spans="1:211" s="85" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="148"/>
+      <c r="A17" s="170"/>
       <c r="B17" s="143" t="s">
         <v>29</v>
       </c>
@@ -7422,11 +7426,11 @@
         <f>IFERROR(L16/M16, 0)</f>
         <v>1</v>
       </c>
-      <c r="N17" s="145">
+      <c r="N17" s="146">
         <f>N16-O16</f>
         <v>0</v>
       </c>
-      <c r="O17" s="146" t="str">
+      <c r="O17" s="168" t="str">
         <f>IF(TEXT(N16-O16,"+0,0; -0,0")="+0,0","0,0",TEXT(N16-O16,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -7621,7 +7625,7 @@
       <c r="GV17" s="102"/>
     </row>
     <row r="18" spans="1:211" s="63" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="175" t="s">
+      <c r="A18" s="148" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="99">
@@ -7778,7 +7782,7 @@
       <c r="DW18" s="55"/>
     </row>
     <row r="19" spans="1:211" s="55" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="175"/>
+      <c r="A19" s="148"/>
       <c r="B19" s="143" t="s">
         <v>35</v>
       </c>
@@ -7823,11 +7827,11 @@
         <f>IFERROR(L18/M18, 0)</f>
         <v>0</v>
       </c>
-      <c r="N19" s="145">
+      <c r="N19" s="146">
         <f>N18-O18</f>
         <v>0</v>
       </c>
-      <c r="O19" s="172" t="str">
+      <c r="O19" s="147" t="str">
         <f>IF(TEXT(N18-O18,"+0,0; -0,0")="+0,0","0,0",TEXT(N18-O18,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -7928,7 +7932,7 @@
       <c r="DF19" s="56"/>
     </row>
     <row r="20" spans="1:211" s="93" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="149" t="s">
+      <c r="A20" s="171" t="s">
         <v>33</v>
       </c>
       <c r="B20" s="99"/>
@@ -8169,14 +8173,14 @@
       <c r="GV20" s="94"/>
     </row>
     <row r="21" spans="1:211" s="85" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="150"/>
+      <c r="A21" s="172"/>
       <c r="B21" s="143"/>
       <c r="C21" s="176">
         <f>C7+C9+C11+C13+C15+C17+C19</f>
         <v>-6.5299999999999994</v>
       </c>
       <c r="D21" s="176">
-        <f t="shared" ref="D21:M21" si="1">D7+D9+D11+D13+D15+D17+D19</f>
+        <f t="shared" ref="D21:J21" si="1">D7+D9+D11+D13+D15+D17+D19</f>
         <v>0</v>
       </c>
       <c r="E21" s="176">
@@ -8204,11 +8208,11 @@
         <v>0</v>
       </c>
       <c r="K21" s="176">
-        <f t="shared" si="1"/>
+        <f>K7+K9+K11+K13+K15+K17+K19</f>
         <v>1</v>
       </c>
-      <c r="L21" s="176">
-        <f t="shared" si="1"/>
+      <c r="L21" s="177">
+        <f>L20-M20</f>
         <v>0</v>
       </c>
       <c r="M21" s="92">
@@ -8313,7 +8317,7 @@
       <c r="DE21" s="86"/>
     </row>
     <row r="22" spans="1:211" s="80" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="175" t="s">
+      <c r="A22" s="148" t="s">
         <v>34</v>
       </c>
       <c r="B22" s="99">
@@ -8455,7 +8459,7 @@
       <c r="FQ22" s="81"/>
     </row>
     <row r="23" spans="1:211" s="55" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="175"/>
+      <c r="A23" s="148"/>
       <c r="B23" s="143" t="s">
         <v>35</v>
       </c>
@@ -8500,11 +8504,11 @@
         <f>IFERROR(L22/M22, 0)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="145">
+      <c r="N23" s="146">
         <f>N22-O22</f>
         <v>0</v>
       </c>
-      <c r="O23" s="172" t="str">
+      <c r="O23" s="147" t="str">
         <f>IF(TEXT(N22-O22,"+0,0; -0,0")="+0,0","0,0",TEXT(N22-O22,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
@@ -8726,19 +8730,19 @@
     <row r="25" spans="1:211" s="55" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="67"/>
       <c r="B25" s="67"/>
-      <c r="C25" s="152" t="s">
+      <c r="C25" s="174" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="153"/>
-      <c r="E25" s="153"/>
-      <c r="F25" s="153"/>
+      <c r="D25" s="175"/>
+      <c r="E25" s="175"/>
+      <c r="F25" s="175"/>
       <c r="G25" s="67"/>
       <c r="H25" s="67"/>
       <c r="I25" s="67"/>
       <c r="J25" s="67"/>
-      <c r="K25" s="151"/>
-      <c r="L25" s="151"/>
-      <c r="M25" s="151"/>
+      <c r="K25" s="173"/>
+      <c r="L25" s="173"/>
+      <c r="M25" s="173"/>
       <c r="N25" s="67"/>
       <c r="O25" s="67"/>
       <c r="P25" s="67"/>
@@ -8939,21 +8943,21 @@
       <c r="HC25" s="62"/>
     </row>
     <row r="26" spans="1:211" s="55" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="151"/>
-      <c r="B26" s="151"/>
-      <c r="C26" s="151"/>
-      <c r="D26" s="151"/>
-      <c r="E26" s="151"/>
-      <c r="F26" s="151"/>
-      <c r="G26" s="151"/>
-      <c r="H26" s="151"/>
-      <c r="I26" s="151"/>
-      <c r="J26" s="151"/>
-      <c r="K26" s="151"/>
-      <c r="L26" s="151"/>
-      <c r="M26" s="151"/>
-      <c r="N26" s="151"/>
-      <c r="O26" s="151"/>
+      <c r="A26" s="173"/>
+      <c r="B26" s="173"/>
+      <c r="C26" s="173"/>
+      <c r="D26" s="173"/>
+      <c r="E26" s="173"/>
+      <c r="F26" s="173"/>
+      <c r="G26" s="173"/>
+      <c r="H26" s="173"/>
+      <c r="I26" s="173"/>
+      <c r="J26" s="173"/>
+      <c r="K26" s="173"/>
+      <c r="L26" s="173"/>
+      <c r="M26" s="173"/>
+      <c r="N26" s="173"/>
+      <c r="O26" s="173"/>
       <c r="P26" s="58"/>
       <c r="Q26" s="58"/>
       <c r="R26" s="58"/>
@@ -57556,18 +57560,12 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A26:O26"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="N23:O23"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="C3:E3"/>
@@ -57582,14 +57580,20 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="I4:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="N19:O19"/>
     <mergeCell ref="N17:O17"/>
     <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A26:O26"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="N23:O23"/>
   </mergeCells>
   <phoneticPr fontId="59" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
